--- a/research/traditional_assets/database/data/morocco/morocco_steel.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_steel.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1211125356863122</v>
+        <v>0.120755575572116</v>
       </c>
       <c r="C2">
-        <v>388.1795733183742</v>
+        <v>385.7596905510181</v>
       </c>
       <c r="D2">
-        <v>310.3795733183742</v>
+        <v>311.8576905510182</v>
       </c>
       <c r="E2">
-        <v>-11.1</v>
+        <v>-7.202</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3.898</v>
       </c>
       <c r="G2">
         <v>77.8</v>
@@ -1451,28 +1451,28 @@
         <v>17.325</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1960694</v>
       </c>
       <c r="N2">
-        <v>17.325</v>
+        <v>17.1289306</v>
       </c>
       <c r="O2">
-        <v>5.543999999999999</v>
+        <v>5.481257791999999</v>
       </c>
       <c r="P2">
-        <v>11.781</v>
+        <v>11.647672808</v>
       </c>
       <c r="Q2">
-        <v>25.581</v>
+        <v>25.447672808</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1211125356863122</v>
+        <v>0.1216298339112283</v>
       </c>
       <c r="T2">
-        <v>0.9815748103161358</v>
+        <v>0.9883169403263881</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>88.36156993391114</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.120755575572116</v>
+        <v>0.1203986154579198</v>
       </c>
       <c r="C3">
-        <v>385.7596905510181</v>
+        <v>383.3539535930158</v>
       </c>
       <c r="D3">
-        <v>311.8576905510182</v>
+        <v>313.3499535930158</v>
       </c>
       <c r="E3">
-        <v>-7.202</v>
+        <v>-3.303999999999999</v>
       </c>
       <c r="F3">
-        <v>3.898</v>
+        <v>7.796</v>
       </c>
       <c r="G3">
         <v>77.8</v>
@@ -1533,28 +1533,28 @@
         <v>17.325</v>
       </c>
       <c r="M3">
-        <v>0.1960694</v>
+        <v>0.3921388</v>
       </c>
       <c r="N3">
-        <v>17.1289306</v>
+        <v>16.93286119999999</v>
       </c>
       <c r="O3">
-        <v>5.481257791999999</v>
+        <v>5.418515583999998</v>
       </c>
       <c r="P3">
-        <v>11.647672808</v>
+        <v>11.514345616</v>
       </c>
       <c r="Q3">
-        <v>25.447672808</v>
+        <v>25.314345616</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1216298339112283</v>
+        <v>0.1221576892427753</v>
       </c>
       <c r="T3">
-        <v>0.9883169403263881</v>
+        <v>0.9951966648266454</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>88.36156993391114</v>
+        <v>44.18078496695556</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1203986154579198</v>
+        <v>0.1200416553437236</v>
       </c>
       <c r="C4">
-        <v>383.3539535930158</v>
+        <v>380.9625664870857</v>
       </c>
       <c r="D4">
-        <v>313.3499535930158</v>
+        <v>314.8565664870857</v>
       </c>
       <c r="E4">
-        <v>-3.303999999999999</v>
+        <v>0.5939999999999994</v>
       </c>
       <c r="F4">
-        <v>7.796</v>
+        <v>11.694</v>
       </c>
       <c r="G4">
         <v>77.8</v>
@@ -1615,28 +1615,28 @@
         <v>17.325</v>
       </c>
       <c r="M4">
-        <v>0.3921388</v>
+        <v>0.5882082</v>
       </c>
       <c r="N4">
-        <v>16.93286119999999</v>
+        <v>16.7367918</v>
       </c>
       <c r="O4">
-        <v>5.418515583999998</v>
+        <v>5.355773375999998</v>
       </c>
       <c r="P4">
-        <v>11.514345616</v>
+        <v>11.381018424</v>
       </c>
       <c r="Q4">
-        <v>25.314345616</v>
+        <v>25.181018424</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1221576892427753</v>
+        <v>0.1226964281894058</v>
       </c>
       <c r="T4">
-        <v>0.9951966648266454</v>
+        <v>1.002218239316599</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>44.18078496695556</v>
+        <v>29.45385664463705</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1200416553437236</v>
+        <v>0.1196846952295274</v>
       </c>
       <c r="C5">
-        <v>380.9625664870857</v>
+        <v>378.585737219123</v>
       </c>
       <c r="D5">
-        <v>314.8565664870857</v>
+        <v>316.377737219123</v>
       </c>
       <c r="E5">
-        <v>0.5939999999999994</v>
+        <v>4.492000000000001</v>
       </c>
       <c r="F5">
-        <v>11.694</v>
+        <v>15.592</v>
       </c>
       <c r="G5">
         <v>77.8</v>
@@ -1697,28 +1697,28 @@
         <v>17.325</v>
       </c>
       <c r="M5">
-        <v>0.5882082</v>
+        <v>0.7842776</v>
       </c>
       <c r="N5">
-        <v>16.7367918</v>
+        <v>16.5407224</v>
       </c>
       <c r="O5">
-        <v>5.355773375999998</v>
+        <v>5.293031167999999</v>
       </c>
       <c r="P5">
-        <v>11.381018424</v>
+        <v>11.247691232</v>
       </c>
       <c r="Q5">
-        <v>25.181018424</v>
+        <v>25.047691232</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1226964281894058</v>
+        <v>0.1232463908640911</v>
       </c>
       <c r="T5">
-        <v>1.002218239316599</v>
+        <v>1.009386096608426</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>29.45385664463705</v>
+        <v>22.09039248347779</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1196846952295274</v>
+        <v>0.1193277351153312</v>
       </c>
       <c r="C6">
-        <v>378.585737219123</v>
+        <v>376.2236778139166</v>
       </c>
       <c r="D6">
-        <v>316.377737219123</v>
+        <v>317.9136778139166</v>
       </c>
       <c r="E6">
-        <v>4.492000000000001</v>
+        <v>8.390000000000002</v>
       </c>
       <c r="F6">
-        <v>15.592</v>
+        <v>19.49</v>
       </c>
       <c r="G6">
         <v>77.8</v>
@@ -1779,28 +1779,28 @@
         <v>17.325</v>
       </c>
       <c r="M6">
-        <v>0.7842776</v>
+        <v>0.9803470000000001</v>
       </c>
       <c r="N6">
-        <v>16.5407224</v>
+        <v>16.34465299999999</v>
       </c>
       <c r="O6">
-        <v>5.293031167999999</v>
+        <v>5.230288959999998</v>
       </c>
       <c r="P6">
-        <v>11.247691232</v>
+        <v>11.11436403999999</v>
       </c>
       <c r="Q6">
-        <v>25.047691232</v>
+        <v>24.91436404</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1232463908640911</v>
+        <v>0.1238079317003487</v>
       </c>
       <c r="T6">
-        <v>1.009386096608426</v>
+        <v>1.016704856159029</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>22.09039248347779</v>
+        <v>17.67231398678222</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1193277351153312</v>
+        <v>0.118970775001135</v>
       </c>
       <c r="C7">
-        <v>376.2236778139166</v>
+        <v>373.8766044336666</v>
       </c>
       <c r="D7">
-        <v>317.9136778139166</v>
+        <v>319.4646044336665</v>
       </c>
       <c r="E7">
-        <v>8.390000000000002</v>
+        <v>12.288</v>
       </c>
       <c r="F7">
-        <v>19.49</v>
+        <v>23.388</v>
       </c>
       <c r="G7">
         <v>77.8</v>
@@ -1861,28 +1861,28 @@
         <v>17.325</v>
       </c>
       <c r="M7">
-        <v>0.9803470000000001</v>
+        <v>1.1764164</v>
       </c>
       <c r="N7">
-        <v>16.34465299999999</v>
+        <v>16.14858359999999</v>
       </c>
       <c r="O7">
-        <v>5.230288959999998</v>
+        <v>5.167546751999999</v>
       </c>
       <c r="P7">
-        <v>11.11436403999999</v>
+        <v>10.981036848</v>
       </c>
       <c r="Q7">
-        <v>24.91436404</v>
+        <v>24.781036848</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1238079317003487</v>
+        <v>0.1243814202139734</v>
       </c>
       <c r="T7">
-        <v>1.016704856159029</v>
+        <v>1.024179333997943</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.67231398678222</v>
+        <v>14.72692832231852</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.118970775001135</v>
+        <v>0.1186852148869388</v>
       </c>
       <c r="C8">
-        <v>373.8766044336666</v>
+        <v>371.2302485300066</v>
       </c>
       <c r="D8">
-        <v>319.4646044336665</v>
+        <v>320.7162485300066</v>
       </c>
       <c r="E8">
-        <v>12.288</v>
+        <v>16.186</v>
       </c>
       <c r="F8">
-        <v>23.388</v>
+        <v>27.286</v>
       </c>
       <c r="G8">
         <v>77.8</v>
@@ -1943,45 +1943,45 @@
         <v>17.325</v>
       </c>
       <c r="M8">
-        <v>1.1764164</v>
+        <v>1.4134148</v>
       </c>
       <c r="N8">
-        <v>16.14858359999999</v>
+        <v>15.9115852</v>
       </c>
       <c r="O8">
-        <v>5.167546751999999</v>
+        <v>5.091707263999999</v>
       </c>
       <c r="P8">
-        <v>10.981036848</v>
+        <v>10.819877936</v>
       </c>
       <c r="Q8">
-        <v>24.781036848</v>
+        <v>24.619877936</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1243814202139734</v>
+        <v>0.1249672418139127</v>
       </c>
       <c r="T8">
-        <v>1.024179333997943</v>
+        <v>1.031814553295757</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0.32</v>
       </c>
       <c r="W8">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.72692832231852</v>
+        <v>12.25754817340246</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1186852148869388</v>
+        <v>0.1183384547727426</v>
       </c>
       <c r="C9">
-        <v>371.2302485300067</v>
+        <v>368.8653884805784</v>
       </c>
       <c r="D9">
-        <v>320.7162485300067</v>
+        <v>322.2493884805784</v>
       </c>
       <c r="E9">
-        <v>16.18600000000001</v>
+        <v>20.084</v>
       </c>
       <c r="F9">
-        <v>27.286</v>
+        <v>31.184</v>
       </c>
       <c r="G9">
         <v>77.8</v>
@@ -2025,28 +2025,28 @@
         <v>17.325</v>
       </c>
       <c r="M9">
-        <v>1.4134148</v>
+        <v>1.6153312</v>
       </c>
       <c r="N9">
-        <v>15.9115852</v>
+        <v>15.7096688</v>
       </c>
       <c r="O9">
-        <v>5.091707263999999</v>
+        <v>5.027094015999999</v>
       </c>
       <c r="P9">
-        <v>10.819877936</v>
+        <v>10.682574784</v>
       </c>
       <c r="Q9">
-        <v>24.619877936</v>
+        <v>24.482574784</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1249672418139127</v>
+        <v>0.1255657986660246</v>
       </c>
       <c r="T9">
-        <v>1.031814553295757</v>
+        <v>1.039615755621786</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>12.25754817340245</v>
+        <v>10.72535465172715</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1183384547727426</v>
+        <v>0.1180957346585464</v>
       </c>
       <c r="C10">
-        <v>368.8653884805784</v>
+        <v>366.0492836814652</v>
       </c>
       <c r="D10">
-        <v>322.2493884805784</v>
+        <v>323.3312836814652</v>
       </c>
       <c r="E10">
-        <v>20.084</v>
+        <v>23.982</v>
       </c>
       <c r="F10">
-        <v>31.184</v>
+        <v>35.082</v>
       </c>
       <c r="G10">
         <v>77.8</v>
@@ -2107,45 +2107,45 @@
         <v>17.325</v>
       </c>
       <c r="M10">
-        <v>1.6153312</v>
+        <v>1.876887</v>
       </c>
       <c r="N10">
-        <v>15.7096688</v>
+        <v>15.448113</v>
       </c>
       <c r="O10">
-        <v>5.027094015999999</v>
+        <v>4.943396159999999</v>
       </c>
       <c r="P10">
-        <v>10.682574784</v>
+        <v>10.50471684</v>
       </c>
       <c r="Q10">
-        <v>24.482574784</v>
+        <v>24.30471684</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1255657986660246</v>
+        <v>0.1261775106137873</v>
       </c>
       <c r="T10">
-        <v>1.039615755621786</v>
+        <v>1.04758841294399</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0.32</v>
       </c>
       <c r="W10">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.72535465172715</v>
+        <v>9.230710213241391</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1180957346585464</v>
+        <v>0.1177605345443502</v>
       </c>
       <c r="C11">
-        <v>366.0492836814652</v>
+        <v>363.6573964959334</v>
       </c>
       <c r="D11">
-        <v>323.3312836814652</v>
+        <v>324.8373964959334</v>
       </c>
       <c r="E11">
-        <v>23.982</v>
+        <v>27.88</v>
       </c>
       <c r="F11">
-        <v>35.082</v>
+        <v>38.98</v>
       </c>
       <c r="G11">
         <v>77.8</v>
@@ -2189,28 +2189,28 @@
         <v>17.325</v>
       </c>
       <c r="M11">
-        <v>1.876887</v>
+        <v>2.08543</v>
       </c>
       <c r="N11">
-        <v>15.448113</v>
+        <v>15.23957</v>
       </c>
       <c r="O11">
-        <v>4.943396159999999</v>
+        <v>4.876662399999999</v>
       </c>
       <c r="P11">
-        <v>10.50471684</v>
+        <v>10.3629076</v>
       </c>
       <c r="Q11">
-        <v>24.30471684</v>
+        <v>24.1629076</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1261775106137873</v>
+        <v>0.1268028161603892</v>
       </c>
       <c r="T11">
-        <v>1.04758841294399</v>
+        <v>1.055738240428911</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>9.230710213241391</v>
+        <v>8.307639191917254</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1177605345443502</v>
+        <v>0.117485174430154</v>
       </c>
       <c r="C12">
-        <v>363.6573964959334</v>
+        <v>361.0071755981727</v>
       </c>
       <c r="D12">
-        <v>324.8373964959334</v>
+        <v>326.0851755981727</v>
       </c>
       <c r="E12">
-        <v>27.88</v>
+        <v>31.778</v>
       </c>
       <c r="F12">
-        <v>38.98</v>
+        <v>42.878</v>
       </c>
       <c r="G12">
         <v>77.8</v>
@@ -2271,45 +2271,45 @@
         <v>17.325</v>
       </c>
       <c r="M12">
-        <v>2.08543</v>
+        <v>2.3282754</v>
       </c>
       <c r="N12">
-        <v>15.23957</v>
+        <v>14.9967246</v>
       </c>
       <c r="O12">
-        <v>4.876662399999999</v>
+        <v>4.798951871999999</v>
       </c>
       <c r="P12">
-        <v>10.3629076</v>
+        <v>10.197772728</v>
       </c>
       <c r="Q12">
-        <v>24.1629076</v>
+        <v>23.997772728</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1268028161603892</v>
+        <v>0.127442173517027</v>
       </c>
       <c r="T12">
-        <v>1.055738240428911</v>
+        <v>1.064071210104503</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0.32</v>
       </c>
       <c r="W12">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>8.307639191917252</v>
+        <v>7.441130031266919</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.117485174430154</v>
+        <v>0.1171554143159578</v>
       </c>
       <c r="C13">
-        <v>361.0071755981727</v>
+        <v>358.6161374142278</v>
       </c>
       <c r="D13">
-        <v>326.0851755981727</v>
+        <v>327.5921374142278</v>
       </c>
       <c r="E13">
-        <v>31.778</v>
+        <v>35.67599999999999</v>
       </c>
       <c r="F13">
-        <v>42.878</v>
+        <v>46.776</v>
       </c>
       <c r="G13">
         <v>77.8</v>
@@ -2353,28 +2353,28 @@
         <v>17.325</v>
       </c>
       <c r="M13">
-        <v>2.3282754</v>
+        <v>2.5399368</v>
       </c>
       <c r="N13">
-        <v>14.9967246</v>
+        <v>14.7850632</v>
       </c>
       <c r="O13">
-        <v>4.798951871999999</v>
+        <v>4.731220223999999</v>
       </c>
       <c r="P13">
-        <v>10.197772728</v>
+        <v>10.053842976</v>
       </c>
       <c r="Q13">
-        <v>23.997772728</v>
+        <v>23.853842976</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.127442173517027</v>
+        <v>0.1280960617226794</v>
       </c>
       <c r="T13">
-        <v>1.064071210104503</v>
+        <v>1.072593565454541</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.441130031266919</v>
+        <v>6.821035861994675</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1171554143159578</v>
+        <v>0.1168256542017616</v>
       </c>
       <c r="C14">
-        <v>358.6161374142278</v>
+        <v>356.239092368569</v>
       </c>
       <c r="D14">
-        <v>327.5921374142278</v>
+        <v>329.113092368569</v>
       </c>
       <c r="E14">
-        <v>35.67599999999999</v>
+        <v>39.57400000000001</v>
       </c>
       <c r="F14">
-        <v>46.776</v>
+        <v>50.67400000000001</v>
       </c>
       <c r="G14">
         <v>77.8</v>
@@ -2435,28 +2435,28 @@
         <v>17.325</v>
       </c>
       <c r="M14">
-        <v>2.5399368</v>
+        <v>2.751598200000001</v>
       </c>
       <c r="N14">
-        <v>14.7850632</v>
+        <v>14.5734018</v>
       </c>
       <c r="O14">
-        <v>4.731220223999999</v>
+        <v>4.663488575999999</v>
       </c>
       <c r="P14">
-        <v>10.053842976</v>
+        <v>9.909913223999997</v>
       </c>
       <c r="Q14">
-        <v>23.853842976</v>
+        <v>23.709913224</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1280960617226794</v>
+        <v>0.1287649818411053</v>
       </c>
       <c r="T14">
-        <v>1.072593565454541</v>
+        <v>1.081311837019522</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.821035861994675</v>
+        <v>6.296340795687391</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1168256542017616</v>
+        <v>0.1165910940875654</v>
       </c>
       <c r="C15">
-        <v>356.239092368569</v>
+        <v>353.4315798871535</v>
       </c>
       <c r="D15">
-        <v>329.113092368569</v>
+        <v>330.2035798871535</v>
       </c>
       <c r="E15">
-        <v>39.57400000000001</v>
+        <v>43.47200000000001</v>
       </c>
       <c r="F15">
-        <v>50.67400000000001</v>
+        <v>54.57200000000001</v>
       </c>
       <c r="G15">
         <v>77.8</v>
@@ -2517,45 +2517,45 @@
         <v>17.325</v>
       </c>
       <c r="M15">
-        <v>2.751598200000001</v>
+        <v>3.017831600000001</v>
       </c>
       <c r="N15">
-        <v>14.5734018</v>
+        <v>14.30716839999999</v>
       </c>
       <c r="O15">
-        <v>4.663488575999999</v>
+        <v>4.578293887999998</v>
       </c>
       <c r="P15">
-        <v>9.909913223999997</v>
+        <v>9.728874511999997</v>
       </c>
       <c r="Q15">
-        <v>23.709913224</v>
+        <v>23.528874512</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1287649818411053</v>
+        <v>0.1294494582413551</v>
       </c>
       <c r="T15">
-        <v>1.081311837019522</v>
+        <v>1.090232859086015</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0.32</v>
       </c>
       <c r="W15">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.296340795687391</v>
+        <v>5.740876992606212</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1165910940875654</v>
+        <v>0.1162681339733693</v>
       </c>
       <c r="C16">
-        <v>353.4315798871535</v>
+        <v>351.0469247120448</v>
       </c>
       <c r="D16">
-        <v>330.2035798871535</v>
+        <v>331.7169247120448</v>
       </c>
       <c r="E16">
-        <v>43.47200000000001</v>
+        <v>47.37000000000001</v>
       </c>
       <c r="F16">
-        <v>54.57200000000001</v>
+        <v>58.47000000000001</v>
       </c>
       <c r="G16">
         <v>77.8</v>
@@ -2599,28 +2599,28 @@
         <v>17.325</v>
       </c>
       <c r="M16">
-        <v>3.017831600000001</v>
+        <v>3.233391000000001</v>
       </c>
       <c r="N16">
-        <v>14.30716839999999</v>
+        <v>14.09160899999999</v>
       </c>
       <c r="O16">
-        <v>4.578293887999998</v>
+        <v>4.509314879999998</v>
       </c>
       <c r="P16">
-        <v>9.728874511999997</v>
+        <v>9.582294119999997</v>
       </c>
       <c r="Q16">
-        <v>23.528874512</v>
+        <v>23.38229412</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1294494582413551</v>
+        <v>0.1301500399686697</v>
       </c>
       <c r="T16">
-        <v>1.090232859086015</v>
+        <v>1.099363787554072</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.740876992606212</v>
+        <v>5.358151859765797</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1162681339733693</v>
+        <v>0.1159451738591731</v>
       </c>
       <c r="C17">
-        <v>351.0469247120448</v>
+        <v>348.6762049223826</v>
       </c>
       <c r="D17">
-        <v>331.7169247120448</v>
+        <v>333.2442049223826</v>
       </c>
       <c r="E17">
-        <v>47.37</v>
+        <v>51.268</v>
       </c>
       <c r="F17">
-        <v>58.47</v>
+        <v>62.368</v>
       </c>
       <c r="G17">
         <v>77.8</v>
@@ -2681,28 +2681,28 @@
         <v>17.325</v>
       </c>
       <c r="M17">
-        <v>3.233391</v>
+        <v>3.4489504</v>
       </c>
       <c r="N17">
-        <v>14.09160899999999</v>
+        <v>13.87604959999999</v>
       </c>
       <c r="O17">
-        <v>4.509314879999998</v>
+        <v>4.440335871999999</v>
       </c>
       <c r="P17">
-        <v>9.582294119999997</v>
+        <v>9.435713727999996</v>
       </c>
       <c r="Q17">
-        <v>23.38229412</v>
+        <v>23.235713728</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1301500399686697</v>
+        <v>0.1308673022133013</v>
       </c>
       <c r="T17">
-        <v>1.099363787554072</v>
+        <v>1.108712119080893</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.358151859765798</v>
+        <v>5.023267368530436</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1159451738591731</v>
+        <v>0.1156222137449768</v>
       </c>
       <c r="C18">
-        <v>348.6762049223826</v>
+        <v>346.3196138910247</v>
       </c>
       <c r="D18">
-        <v>333.2442049223826</v>
+        <v>334.7856138910248</v>
       </c>
       <c r="E18">
-        <v>51.268</v>
+        <v>55.166</v>
       </c>
       <c r="F18">
-        <v>62.368</v>
+        <v>66.26600000000001</v>
       </c>
       <c r="G18">
         <v>77.8</v>
@@ -2763,28 +2763,28 @@
         <v>17.325</v>
       </c>
       <c r="M18">
-        <v>3.4489504</v>
+        <v>3.6645098</v>
       </c>
       <c r="N18">
-        <v>13.87604959999999</v>
+        <v>13.66049019999999</v>
       </c>
       <c r="O18">
-        <v>4.440335871999999</v>
+        <v>4.371356863999998</v>
       </c>
       <c r="P18">
-        <v>9.435713727999996</v>
+        <v>9.289133335999995</v>
       </c>
       <c r="Q18">
-        <v>23.235713728</v>
+        <v>23.089133336</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1308673022133013</v>
+        <v>0.1316018478855143</v>
       </c>
       <c r="T18">
-        <v>1.108712119080893</v>
+        <v>1.118285711608359</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.023267368530436</v>
+        <v>4.727781052734528</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1156222137449768</v>
+        <v>0.1156052536307806</v>
       </c>
       <c r="C19">
-        <v>346.3196138910247</v>
+        <v>342.5029545057708</v>
       </c>
       <c r="D19">
-        <v>334.7856138910248</v>
+        <v>334.8669545057709</v>
       </c>
       <c r="E19">
-        <v>55.166</v>
+        <v>59.06400000000001</v>
       </c>
       <c r="F19">
-        <v>66.26600000000001</v>
+        <v>70.16400000000002</v>
       </c>
       <c r="G19">
         <v>77.8</v>
@@ -2845,45 +2845,45 @@
         <v>17.325</v>
       </c>
       <c r="M19">
-        <v>3.6645098</v>
+        <v>4.055479200000002</v>
       </c>
       <c r="N19">
-        <v>13.66049019999999</v>
+        <v>13.2695208</v>
       </c>
       <c r="O19">
-        <v>4.371356863999998</v>
+        <v>4.246246655999999</v>
       </c>
       <c r="P19">
-        <v>9.289133335999995</v>
+        <v>9.023274143999997</v>
       </c>
       <c r="Q19">
-        <v>23.089133336</v>
+        <v>22.823274144</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1316018478855143</v>
+        <v>0.13235430930583</v>
       </c>
       <c r="T19">
-        <v>1.118285711608359</v>
+        <v>1.128092806392593</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0.32</v>
       </c>
       <c r="W19">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.727781052734528</v>
+        <v>4.271998238827113</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1156052536307806</v>
+        <v>0.1152992935165845</v>
       </c>
       <c r="C20">
-        <v>342.5029545057708</v>
+        <v>340.0791555581408</v>
       </c>
       <c r="D20">
-        <v>334.8669545057708</v>
+        <v>336.3411555581408</v>
       </c>
       <c r="E20">
-        <v>59.064</v>
+        <v>62.962</v>
       </c>
       <c r="F20">
-        <v>70.164</v>
+        <v>74.062</v>
       </c>
       <c r="G20">
         <v>77.8</v>
@@ -2927,28 +2927,28 @@
         <v>17.325</v>
       </c>
       <c r="M20">
-        <v>4.055479200000001</v>
+        <v>4.2807836</v>
       </c>
       <c r="N20">
-        <v>13.2695208</v>
+        <v>13.0442164</v>
       </c>
       <c r="O20">
-        <v>4.246246655999999</v>
+        <v>4.174149247999999</v>
       </c>
       <c r="P20">
-        <v>9.023274143999997</v>
+        <v>8.870067151999997</v>
       </c>
       <c r="Q20">
-        <v>22.823274144</v>
+        <v>22.670067152</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.13235430930583</v>
+        <v>0.1331253500204746</v>
       </c>
       <c r="T20">
-        <v>1.128092806392593</v>
+        <v>1.138142051665327</v>
       </c>
       <c r="U20">
         <v>0.0578</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.271998238827114</v>
+        <v>4.047156226257266</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1152992935165845</v>
+        <v>0.1154693334023883</v>
       </c>
       <c r="C21">
-        <v>340.0791555581408</v>
+        <v>335.3602576265945</v>
       </c>
       <c r="D21">
-        <v>336.3411555581408</v>
+        <v>335.5202576265945</v>
       </c>
       <c r="E21">
-        <v>62.962</v>
+        <v>66.86000000000001</v>
       </c>
       <c r="F21">
-        <v>74.062</v>
+        <v>77.96000000000001</v>
       </c>
       <c r="G21">
         <v>77.8</v>
@@ -3009,45 +3009,45 @@
         <v>17.325</v>
       </c>
       <c r="M21">
-        <v>4.2807836</v>
+        <v>4.778948000000001</v>
       </c>
       <c r="N21">
-        <v>13.0442164</v>
+        <v>12.546052</v>
       </c>
       <c r="O21">
-        <v>4.174149247999999</v>
+        <v>4.014736639999999</v>
       </c>
       <c r="P21">
-        <v>8.870067151999997</v>
+        <v>8.531315359999997</v>
       </c>
       <c r="Q21">
-        <v>22.670067152</v>
+        <v>22.33131536</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1331253500204746</v>
+        <v>0.1339156667529853</v>
       </c>
       <c r="T21">
-        <v>1.138142051665327</v>
+        <v>1.148442528069879</v>
       </c>
       <c r="U21">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V21">
         <v>0.32</v>
       </c>
       <c r="W21">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.047156226257266</v>
+        <v>3.625274851285261</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1154693334023883</v>
+        <v>0.1155870132881921</v>
       </c>
       <c r="C22">
-        <v>335.3602576265945</v>
+        <v>330.8964792139361</v>
       </c>
       <c r="D22">
-        <v>335.5202576265945</v>
+        <v>334.9544792139361</v>
       </c>
       <c r="E22">
-        <v>66.86000000000001</v>
+        <v>70.75800000000001</v>
       </c>
       <c r="F22">
-        <v>77.96000000000001</v>
+        <v>81.858</v>
       </c>
       <c r="G22">
         <v>77.8</v>
@@ -3091,45 +3091,45 @@
         <v>17.325</v>
       </c>
       <c r="M22">
-        <v>4.778948000000001</v>
+        <v>5.247097800000001</v>
       </c>
       <c r="N22">
-        <v>12.546052</v>
+        <v>12.0779022</v>
       </c>
       <c r="O22">
-        <v>4.014736639999999</v>
+        <v>3.864928703999999</v>
       </c>
       <c r="P22">
-        <v>8.531315359999997</v>
+        <v>8.212973495999996</v>
       </c>
       <c r="Q22">
-        <v>22.33131536</v>
+        <v>22.012973496</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1339156667529853</v>
+        <v>0.1347259915040406</v>
       </c>
       <c r="T22">
-        <v>1.148442528069879</v>
+        <v>1.159003776028977</v>
       </c>
       <c r="U22">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V22">
         <v>0.32</v>
       </c>
       <c r="W22">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.625274851285261</v>
+        <v>3.301825248997645</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1155870132881921</v>
+        <v>0.1153238931739959</v>
       </c>
       <c r="C23">
-        <v>330.8964792139361</v>
+        <v>328.2661478785884</v>
       </c>
       <c r="D23">
-        <v>334.9544792139361</v>
+        <v>336.2221478785884</v>
       </c>
       <c r="E23">
-        <v>70.75800000000001</v>
+        <v>74.65600000000001</v>
       </c>
       <c r="F23">
-        <v>81.858</v>
+        <v>85.756</v>
       </c>
       <c r="G23">
         <v>77.8</v>
@@ -3173,28 +3173,28 @@
         <v>17.325</v>
       </c>
       <c r="M23">
-        <v>5.247097800000001</v>
+        <v>5.4969596</v>
       </c>
       <c r="N23">
-        <v>12.0779022</v>
+        <v>11.8280404</v>
       </c>
       <c r="O23">
-        <v>3.864928703999999</v>
+        <v>3.784972927999998</v>
       </c>
       <c r="P23">
-        <v>8.212973495999996</v>
+        <v>8.043067471999997</v>
       </c>
       <c r="Q23">
-        <v>22.012973496</v>
+        <v>21.843067472</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1347259915040406</v>
+        <v>0.1355570938128152</v>
       </c>
       <c r="T23">
-        <v>1.159003776028977</v>
+        <v>1.169835825217795</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.301825248997645</v>
+        <v>3.151742283134116</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1153238931739959</v>
+        <v>0.1150607730597997</v>
       </c>
       <c r="C24">
-        <v>328.2661478785884</v>
+        <v>325.6454482325524</v>
       </c>
       <c r="D24">
-        <v>336.2221478785884</v>
+        <v>337.4994482325524</v>
       </c>
       <c r="E24">
-        <v>74.65600000000001</v>
+        <v>78.55400000000002</v>
       </c>
       <c r="F24">
-        <v>85.756</v>
+        <v>89.65400000000001</v>
       </c>
       <c r="G24">
         <v>77.8</v>
@@ -3255,28 +3255,28 @@
         <v>17.325</v>
       </c>
       <c r="M24">
-        <v>5.4969596</v>
+        <v>5.746821400000001</v>
       </c>
       <c r="N24">
-        <v>11.8280404</v>
+        <v>11.57817859999999</v>
       </c>
       <c r="O24">
-        <v>3.784972927999998</v>
+        <v>3.705017151999998</v>
       </c>
       <c r="P24">
-        <v>8.043067471999997</v>
+        <v>7.873161447999996</v>
       </c>
       <c r="Q24">
-        <v>21.843067472</v>
+        <v>21.67316144799999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1355570938128152</v>
+        <v>0.136409783194545</v>
       </c>
       <c r="T24">
-        <v>1.169835825217795</v>
+        <v>1.180949226333595</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.151742283134116</v>
+        <v>3.014710009954371</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1150607730597997</v>
+        <v>0.1160706129456034</v>
       </c>
       <c r="C25">
-        <v>325.6454482325524</v>
+        <v>316.8973353621007</v>
       </c>
       <c r="D25">
-        <v>337.4994482325524</v>
+        <v>332.6493353621007</v>
       </c>
       <c r="E25">
-        <v>78.55400000000002</v>
+        <v>82.45200000000001</v>
       </c>
       <c r="F25">
-        <v>89.65400000000001</v>
+        <v>93.55200000000001</v>
       </c>
       <c r="G25">
         <v>77.8</v>
@@ -3337,45 +3337,45 @@
         <v>17.325</v>
       </c>
       <c r="M25">
-        <v>5.746821400000001</v>
+        <v>6.726388800000001</v>
       </c>
       <c r="N25">
-        <v>11.57817859999999</v>
+        <v>10.59861119999999</v>
       </c>
       <c r="O25">
-        <v>3.705017151999998</v>
+        <v>3.391555583999998</v>
       </c>
       <c r="P25">
-        <v>7.873161447999996</v>
+        <v>7.207055615999995</v>
       </c>
       <c r="Q25">
-        <v>21.67316144799999</v>
+        <v>21.007055616</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.136409783194545</v>
+        <v>0.1372849117705308</v>
       </c>
       <c r="T25">
-        <v>1.180949226333595</v>
+        <v>1.192355085373495</v>
       </c>
       <c r="U25">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V25">
         <v>0.32</v>
       </c>
       <c r="W25">
-        <v>0.043588</v>
+        <v>0.048892</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.014710009954371</v>
+        <v>2.575676267776848</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1160706129456034</v>
+        <v>0.1165235328314072</v>
       </c>
       <c r="C26">
-        <v>316.8973353621008</v>
+        <v>310.8690190027063</v>
       </c>
       <c r="D26">
-        <v>332.6493353621008</v>
+        <v>330.5190190027063</v>
       </c>
       <c r="E26">
-        <v>82.452</v>
+        <v>86.35000000000001</v>
       </c>
       <c r="F26">
-        <v>93.55199999999999</v>
+        <v>97.45</v>
       </c>
       <c r="G26">
         <v>77.8</v>
@@ -3419,45 +3419,45 @@
         <v>17.325</v>
       </c>
       <c r="M26">
-        <v>6.7263888</v>
+        <v>7.386710000000001</v>
       </c>
       <c r="N26">
-        <v>10.5986112</v>
+        <v>9.938289999999995</v>
       </c>
       <c r="O26">
-        <v>3.391555583999999</v>
+        <v>3.180252799999999</v>
       </c>
       <c r="P26">
-        <v>7.207055615999998</v>
+        <v>6.758037199999997</v>
       </c>
       <c r="Q26">
-        <v>21.007055616</v>
+        <v>20.5580372</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1372849117705308</v>
+        <v>0.138183377108543</v>
       </c>
       <c r="T26">
-        <v>1.192355085373495</v>
+        <v>1.20406510065446</v>
       </c>
       <c r="U26">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V26">
         <v>0.32</v>
       </c>
       <c r="W26">
-        <v>0.048892</v>
+        <v>0.051544</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.575676267776849</v>
+        <v>2.345428478984554</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1165235328314072</v>
+        <v>0.1163399727172111</v>
       </c>
       <c r="C27">
-        <v>310.8690190027063</v>
+        <v>307.831100266352</v>
       </c>
       <c r="D27">
-        <v>330.5190190027063</v>
+        <v>331.379100266352</v>
       </c>
       <c r="E27">
-        <v>86.35000000000001</v>
+        <v>90.24800000000002</v>
       </c>
       <c r="F27">
-        <v>97.45</v>
+        <v>101.348</v>
       </c>
       <c r="G27">
         <v>77.8</v>
@@ -3501,28 +3501,28 @@
         <v>17.325</v>
       </c>
       <c r="M27">
-        <v>7.386710000000001</v>
+        <v>7.682178400000002</v>
       </c>
       <c r="N27">
-        <v>9.938289999999995</v>
+        <v>9.642821599999994</v>
       </c>
       <c r="O27">
-        <v>3.180252799999999</v>
+        <v>3.085702911999998</v>
       </c>
       <c r="P27">
-        <v>6.758037199999997</v>
+        <v>6.557118687999996</v>
       </c>
       <c r="Q27">
-        <v>20.5580372</v>
+        <v>20.357118688</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.138183377108543</v>
+        <v>0.1391061252935284</v>
       </c>
       <c r="T27">
-        <v>1.20406510065446</v>
+        <v>1.21609160283491</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.345428478984554</v>
+        <v>2.255219691331302</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1163399727172111</v>
+        <v>0.1161564126030149</v>
       </c>
       <c r="C28">
-        <v>307.831100266352</v>
+        <v>304.7976694397455</v>
       </c>
       <c r="D28">
-        <v>331.379100266352</v>
+        <v>332.2436694397455</v>
       </c>
       <c r="E28">
-        <v>90.24800000000002</v>
+        <v>94.14600000000002</v>
       </c>
       <c r="F28">
-        <v>101.348</v>
+        <v>105.246</v>
       </c>
       <c r="G28">
         <v>77.8</v>
@@ -3583,28 +3583,28 @@
         <v>17.325</v>
       </c>
       <c r="M28">
-        <v>7.682178400000002</v>
+        <v>7.977646800000001</v>
       </c>
       <c r="N28">
-        <v>9.642821599999994</v>
+        <v>9.347353199999993</v>
       </c>
       <c r="O28">
-        <v>3.085702911999998</v>
+        <v>2.991153023999998</v>
       </c>
       <c r="P28">
-        <v>6.557118687999996</v>
+        <v>6.356200175999995</v>
       </c>
       <c r="Q28">
-        <v>20.357118688</v>
+        <v>20.156200176</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1391061252935284</v>
+        <v>0.1400541542507053</v>
       </c>
       <c r="T28">
-        <v>1.21609160283491</v>
+        <v>1.228447598225783</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.255219691331302</v>
+        <v>2.171693036096809</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1161564126030149</v>
+        <v>0.1159728524888187</v>
       </c>
       <c r="C29">
-        <v>304.7976694397455</v>
+        <v>301.7687617416873</v>
       </c>
       <c r="D29">
-        <v>332.2436694397455</v>
+        <v>333.1127617416873</v>
       </c>
       <c r="E29">
-        <v>94.14600000000002</v>
+        <v>98.04400000000003</v>
       </c>
       <c r="F29">
-        <v>105.246</v>
+        <v>109.144</v>
       </c>
       <c r="G29">
         <v>77.8</v>
@@ -3665,28 +3665,28 @@
         <v>17.325</v>
       </c>
       <c r="M29">
-        <v>7.977646800000001</v>
+        <v>8.273115200000003</v>
       </c>
       <c r="N29">
-        <v>9.347353199999993</v>
+        <v>9.051884799999993</v>
       </c>
       <c r="O29">
-        <v>2.991153023999998</v>
+        <v>2.896603135999998</v>
       </c>
       <c r="P29">
-        <v>6.356200175999995</v>
+        <v>6.155281663999995</v>
       </c>
       <c r="Q29">
-        <v>20.156200176</v>
+        <v>19.955281664</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1400541542507053</v>
+        <v>0.1410285173455815</v>
       </c>
       <c r="T29">
-        <v>1.228447598225783</v>
+        <v>1.241146815710847</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.171693036096809</v>
+        <v>2.094132570521922</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1159728524888187</v>
+        <v>0.1157892923746225</v>
       </c>
       <c r="C30">
-        <v>301.7687617416873</v>
+        <v>298.7444127604492</v>
       </c>
       <c r="D30">
-        <v>333.1127617416873</v>
+        <v>333.9864127604492</v>
       </c>
       <c r="E30">
-        <v>98.04400000000003</v>
+        <v>101.942</v>
       </c>
       <c r="F30">
-        <v>109.144</v>
+        <v>113.042</v>
       </c>
       <c r="G30">
         <v>77.8</v>
@@ -3747,28 +3747,28 @@
         <v>17.325</v>
       </c>
       <c r="M30">
-        <v>8.273115200000003</v>
+        <v>8.568583600000002</v>
       </c>
       <c r="N30">
-        <v>9.051884799999993</v>
+        <v>8.756416399999994</v>
       </c>
       <c r="O30">
-        <v>2.896603135999998</v>
+        <v>2.802053247999998</v>
       </c>
       <c r="P30">
-        <v>6.155281663999995</v>
+        <v>5.954363151999996</v>
       </c>
       <c r="Q30">
-        <v>19.955281664</v>
+        <v>19.754363152</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1410285173455815</v>
+        <v>0.1420303272882006</v>
       </c>
       <c r="T30">
-        <v>1.241146815710847</v>
+        <v>1.25420375763211</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.094132570521922</v>
+        <v>2.021921102572891</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1157892923746225</v>
+        <v>0.1185025322604262</v>
       </c>
       <c r="C31">
-        <v>298.7444127604492</v>
+        <v>282.3821253657247</v>
       </c>
       <c r="D31">
-        <v>333.9864127604492</v>
+        <v>321.5221253657247</v>
       </c>
       <c r="E31">
-        <v>101.942</v>
+        <v>105.84</v>
       </c>
       <c r="F31">
-        <v>113.042</v>
+        <v>116.94</v>
       </c>
       <c r="G31">
         <v>77.8</v>
@@ -3829,45 +3829,45 @@
         <v>17.325</v>
       </c>
       <c r="M31">
-        <v>8.5685836</v>
+        <v>10.5246</v>
       </c>
       <c r="N31">
-        <v>8.756416399999996</v>
+        <v>6.800399999999996</v>
       </c>
       <c r="O31">
-        <v>2.802053247999999</v>
+        <v>2.176127999999999</v>
       </c>
       <c r="P31">
-        <v>5.954363151999997</v>
+        <v>4.624271999999998</v>
       </c>
       <c r="Q31">
-        <v>19.754363152</v>
+        <v>18.424272</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1420303272882006</v>
+        <v>0.1430607603720375</v>
       </c>
       <c r="T31">
-        <v>1.25420375763211</v>
+        <v>1.267633755036838</v>
       </c>
       <c r="U31">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V31">
         <v>0.32</v>
       </c>
       <c r="W31">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>2.021921102572891</v>
+        <v>1.646143321361381</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1185025322604262</v>
+        <v>0.11841553214623</v>
       </c>
       <c r="C32">
-        <v>282.3821253657247</v>
+        <v>278.8693385673176</v>
       </c>
       <c r="D32">
-        <v>321.5221253657247</v>
+        <v>321.9073385673177</v>
       </c>
       <c r="E32">
-        <v>105.84</v>
+        <v>109.738</v>
       </c>
       <c r="F32">
-        <v>116.94</v>
+        <v>120.838</v>
       </c>
       <c r="G32">
         <v>77.8</v>
@@ -3911,28 +3911,28 @@
         <v>17.325</v>
       </c>
       <c r="M32">
-        <v>10.5246</v>
+        <v>10.87542</v>
       </c>
       <c r="N32">
-        <v>6.800399999999996</v>
+        <v>6.449579999999996</v>
       </c>
       <c r="O32">
-        <v>2.176127999999999</v>
+        <v>2.063865599999999</v>
       </c>
       <c r="P32">
-        <v>4.624271999999998</v>
+        <v>4.385714399999997</v>
       </c>
       <c r="Q32">
-        <v>18.424272</v>
+        <v>18.1857144</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1430607603720375</v>
+        <v>0.1441210610814928</v>
       </c>
       <c r="T32">
-        <v>1.267633755036838</v>
+        <v>1.28145302772866</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.646143321361381</v>
+        <v>1.593041923898111</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.11841553214623</v>
+        <v>0.1183285320320339</v>
       </c>
       <c r="C33">
-        <v>278.8693385673176</v>
+        <v>275.3574759181133</v>
       </c>
       <c r="D33">
-        <v>321.9073385673177</v>
+        <v>322.2934759181133</v>
       </c>
       <c r="E33">
-        <v>109.738</v>
+        <v>113.636</v>
       </c>
       <c r="F33">
-        <v>120.838</v>
+        <v>124.736</v>
       </c>
       <c r="G33">
         <v>77.8</v>
@@ -3993,28 +3993,28 @@
         <v>17.325</v>
       </c>
       <c r="M33">
-        <v>10.87542</v>
+        <v>11.22624</v>
       </c>
       <c r="N33">
-        <v>6.449579999999996</v>
+        <v>6.098759999999995</v>
       </c>
       <c r="O33">
-        <v>2.063865599999999</v>
+        <v>1.951603199999999</v>
       </c>
       <c r="P33">
-        <v>4.385714399999997</v>
+        <v>4.147156799999997</v>
       </c>
       <c r="Q33">
-        <v>18.1857144</v>
+        <v>17.9471568</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1441210610814928</v>
+        <v>0.1452125471059321</v>
       </c>
       <c r="T33">
-        <v>1.28145302772866</v>
+        <v>1.295678749617299</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.593041923898111</v>
+        <v>1.543259363776295</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1183285320320339</v>
+        <v>0.1329232227387636</v>
       </c>
       <c r="C34">
-        <v>275.3574759181133</v>
+        <v>217.4695814909313</v>
       </c>
       <c r="D34">
-        <v>322.2934759181133</v>
+        <v>268.3035814909313</v>
       </c>
       <c r="E34">
-        <v>113.636</v>
+        <v>117.534</v>
       </c>
       <c r="F34">
-        <v>124.736</v>
+        <v>128.634</v>
       </c>
       <c r="G34">
         <v>77.8</v>
@@ -4075,45 +4075,45 @@
         <v>17.325</v>
       </c>
       <c r="M34">
-        <v>11.22624</v>
+        <v>18.8834712</v>
       </c>
       <c r="N34">
-        <v>6.098759999999995</v>
+        <v>-1.558471200000007</v>
       </c>
       <c r="O34">
-        <v>1.951603199999999</v>
+        <v>-0.4987107840000022</v>
       </c>
       <c r="P34">
-        <v>4.147156799999997</v>
+        <v>-1.059760416000004</v>
       </c>
       <c r="Q34">
-        <v>17.9471568</v>
+        <v>12.740239584</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1452125471059321</v>
+        <v>0.147316270201979</v>
       </c>
       <c r="T34">
-        <v>1.295678749617299</v>
+        <v>1.3230973138728</v>
       </c>
       <c r="U34">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V34">
-        <v>0.32</v>
+        <v>0.2935900895170162</v>
       </c>
       <c r="W34">
-        <v>0.06119999999999999</v>
+        <v>0.103700974858902</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.543259363776295</v>
+        <v>0.9174690297406757</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1329232227387636</v>
+        <v>0.1339332227387636</v>
       </c>
       <c r="C35">
-        <v>217.4695814909313</v>
+        <v>210.4968429430278</v>
       </c>
       <c r="D35">
-        <v>268.3035814909313</v>
+        <v>265.2288429430278</v>
       </c>
       <c r="E35">
-        <v>117.534</v>
+        <v>121.432</v>
       </c>
       <c r="F35">
-        <v>128.634</v>
+        <v>132.532</v>
       </c>
       <c r="G35">
         <v>77.8</v>
@@ -4157,37 +4157,37 @@
         <v>17.325</v>
       </c>
       <c r="M35">
-        <v>18.8834712</v>
+        <v>19.4556976</v>
       </c>
       <c r="N35">
-        <v>-1.558471200000007</v>
+        <v>-2.130697600000008</v>
       </c>
       <c r="O35">
-        <v>-0.4987107840000022</v>
+        <v>-0.6818232320000027</v>
       </c>
       <c r="P35">
-        <v>-1.059760416000004</v>
+        <v>-1.448874368000006</v>
       </c>
       <c r="Q35">
-        <v>12.740239584</v>
+        <v>12.351125632</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.147316270201979</v>
+        <v>0.1488543955080696</v>
       </c>
       <c r="T35">
-        <v>1.3230973138728</v>
+        <v>1.343144242870873</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
       </c>
       <c r="V35">
-        <v>0.2935900895170162</v>
+        <v>0.2849550868841628</v>
       </c>
       <c r="W35">
-        <v>0.103700974858902</v>
+        <v>0.1049685932454049</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.9174690297406757</v>
+        <v>0.8904846465130087</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1339332227387636</v>
+        <v>0.1349432227387636</v>
       </c>
       <c r="C36">
-        <v>210.4968429430278</v>
+        <v>203.5937784732645</v>
       </c>
       <c r="D36">
-        <v>265.2288429430278</v>
+        <v>262.2237784732645</v>
       </c>
       <c r="E36">
-        <v>121.432</v>
+        <v>125.33</v>
       </c>
       <c r="F36">
-        <v>132.532</v>
+        <v>136.43</v>
       </c>
       <c r="G36">
         <v>77.8</v>
@@ -4239,37 +4239,37 @@
         <v>17.325</v>
       </c>
       <c r="M36">
-        <v>19.4556976</v>
+        <v>20.027924</v>
       </c>
       <c r="N36">
-        <v>-2.130697600000008</v>
+        <v>-2.702924000000007</v>
       </c>
       <c r="O36">
-        <v>-0.6818232320000027</v>
+        <v>-0.8649356800000021</v>
       </c>
       <c r="P36">
-        <v>-1.448874368000006</v>
+        <v>-1.837988320000004</v>
       </c>
       <c r="Q36">
-        <v>12.351125632</v>
+        <v>11.96201168</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1488543955080696</v>
+        <v>0.1504398477466553</v>
       </c>
       <c r="T36">
-        <v>1.343144242870873</v>
+        <v>1.363808000453502</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.2849550868841628</v>
+        <v>0.2768135129731867</v>
       </c>
       <c r="W36">
-        <v>0.1049685932454049</v>
+        <v>0.1061637762955362</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8904846465130087</v>
+        <v>0.8650422280412086</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1349432227387636</v>
+        <v>0.1359532227387636</v>
       </c>
       <c r="C37">
-        <v>203.5937784732645</v>
+        <v>196.7580463743749</v>
       </c>
       <c r="D37">
-        <v>262.2237784732645</v>
+        <v>259.286046374375</v>
       </c>
       <c r="E37">
-        <v>125.33</v>
+        <v>129.228</v>
       </c>
       <c r="F37">
-        <v>136.43</v>
+        <v>140.328</v>
       </c>
       <c r="G37">
         <v>77.8</v>
@@ -4321,37 +4321,37 @@
         <v>17.325</v>
       </c>
       <c r="M37">
-        <v>20.027924</v>
+        <v>20.60015040000001</v>
       </c>
       <c r="N37">
-        <v>-2.702924000000007</v>
+        <v>-3.275150400000012</v>
       </c>
       <c r="O37">
-        <v>-0.8649356800000021</v>
+        <v>-1.048048128000004</v>
       </c>
       <c r="P37">
-        <v>-1.837988320000004</v>
+        <v>-2.227102272000008</v>
       </c>
       <c r="Q37">
-        <v>11.96201168</v>
+        <v>11.57289772799999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1504398477466553</v>
+        <v>0.1520748453676968</v>
       </c>
       <c r="T37">
-        <v>1.363808000453502</v>
+        <v>1.385117500460588</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.2768135129731867</v>
+        <v>0.2691242487239315</v>
       </c>
       <c r="W37">
-        <v>0.1061637762955362</v>
+        <v>0.1072925602873269</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8650422280412086</v>
+        <v>0.8410132772622859</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1359532227387636</v>
+        <v>0.1369632227387636</v>
       </c>
       <c r="C38">
-        <v>196.7580463743749</v>
+        <v>189.9874087144651</v>
       </c>
       <c r="D38">
-        <v>259.2860463743749</v>
+        <v>256.4134087144651</v>
       </c>
       <c r="E38">
-        <v>129.228</v>
+        <v>133.126</v>
       </c>
       <c r="F38">
-        <v>140.328</v>
+        <v>144.226</v>
       </c>
       <c r="G38">
         <v>77.8</v>
@@ -4403,37 +4403,37 @@
         <v>17.325</v>
       </c>
       <c r="M38">
-        <v>20.6001504</v>
+        <v>21.1723768</v>
       </c>
       <c r="N38">
-        <v>-3.275150400000008</v>
+        <v>-3.847376800000006</v>
       </c>
       <c r="O38">
-        <v>-1.048048128000003</v>
+        <v>-1.231160576000002</v>
       </c>
       <c r="P38">
-        <v>-2.227102272000006</v>
+        <v>-2.616216224000004</v>
       </c>
       <c r="Q38">
-        <v>11.572897728</v>
+        <v>11.183783776</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1520748453676968</v>
+        <v>0.1537617476751205</v>
       </c>
       <c r="T38">
-        <v>1.385117500460588</v>
+        <v>1.407103492531391</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.2691242487239315</v>
+        <v>0.2618506203800415</v>
       </c>
       <c r="W38">
-        <v>0.1072925602873269</v>
+        <v>0.1083603289282099</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.841013277262286</v>
+        <v>0.8182831886876297</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1369632227387636</v>
+        <v>0.160455465124985</v>
       </c>
       <c r="C39">
-        <v>189.9874087144651</v>
+        <v>133.5517826882565</v>
       </c>
       <c r="D39">
-        <v>256.4134087144651</v>
+        <v>203.8757826882565</v>
       </c>
       <c r="E39">
-        <v>133.126</v>
+        <v>137.024</v>
       </c>
       <c r="F39">
-        <v>144.226</v>
+        <v>148.124</v>
       </c>
       <c r="G39">
         <v>77.8</v>
@@ -4485,45 +4485,45 @@
         <v>17.325</v>
       </c>
       <c r="M39">
-        <v>21.1723768</v>
+        <v>29.7432992</v>
       </c>
       <c r="N39">
-        <v>-3.847376800000006</v>
+        <v>-12.4182992</v>
       </c>
       <c r="O39">
-        <v>-1.231160576000002</v>
+        <v>-3.973855744000001</v>
       </c>
       <c r="P39">
-        <v>-2.616216224000004</v>
+        <v>-8.444443456000002</v>
       </c>
       <c r="Q39">
-        <v>11.183783776</v>
+        <v>5.355556543999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1537617476751205</v>
+        <v>0.1586679732605602</v>
       </c>
       <c r="T39">
-        <v>1.407103492531391</v>
+        <v>1.471048059056873</v>
       </c>
       <c r="U39">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V39">
-        <v>0.2618506203800415</v>
+        <v>0.1863949242053148</v>
       </c>
       <c r="W39">
-        <v>0.1083603289282099</v>
+        <v>0.1633718992195728</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y39">
-        <v>0.8182831886876297</v>
+        <v>0.5824841381416086</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.160455465124985</v>
+        <v>0.162005465124985</v>
       </c>
       <c r="C40">
-        <v>133.5517826882565</v>
+        <v>126.9343971341698</v>
       </c>
       <c r="D40">
-        <v>203.8757826882565</v>
+        <v>201.1563971341699</v>
       </c>
       <c r="E40">
-        <v>137.024</v>
+        <v>140.922</v>
       </c>
       <c r="F40">
-        <v>148.124</v>
+        <v>152.022</v>
       </c>
       <c r="G40">
         <v>77.8</v>
@@ -4567,37 +4567,37 @@
         <v>17.325</v>
       </c>
       <c r="M40">
-        <v>29.7432992</v>
+        <v>30.52601760000001</v>
       </c>
       <c r="N40">
-        <v>-12.4182992</v>
+        <v>-13.20101760000001</v>
       </c>
       <c r="O40">
-        <v>-3.973855744000001</v>
+        <v>-4.224325632000004</v>
       </c>
       <c r="P40">
-        <v>-8.444443456000002</v>
+        <v>-8.976691968000008</v>
       </c>
       <c r="Q40">
-        <v>5.355556543999999</v>
+        <v>4.823308031999993</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1586679732605602</v>
+        <v>0.160518267904176</v>
       </c>
       <c r="T40">
-        <v>1.471048059056873</v>
+        <v>1.495163601008625</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
       </c>
       <c r="V40">
-        <v>0.1863949242053148</v>
+        <v>0.1816155671744092</v>
       </c>
       <c r="W40">
-        <v>0.1633718992195728</v>
+        <v>0.1643315941113787</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5824841381416086</v>
+        <v>0.5675486474200288</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.162005465124985</v>
+        <v>0.163555465124985</v>
       </c>
       <c r="C41">
-        <v>126.9343971341698</v>
+        <v>120.3886014227179</v>
       </c>
       <c r="D41">
-        <v>201.1563971341699</v>
+        <v>198.5086014227179</v>
       </c>
       <c r="E41">
-        <v>140.922</v>
+        <v>144.82</v>
       </c>
       <c r="F41">
-        <v>152.022</v>
+        <v>155.92</v>
       </c>
       <c r="G41">
         <v>77.8</v>
@@ -4649,37 +4649,37 @@
         <v>17.325</v>
       </c>
       <c r="M41">
-        <v>30.52601760000001</v>
+        <v>31.308736</v>
       </c>
       <c r="N41">
-        <v>-13.20101760000001</v>
+        <v>-13.98373600000001</v>
       </c>
       <c r="O41">
-        <v>-4.224325632000004</v>
+        <v>-4.474795520000002</v>
       </c>
       <c r="P41">
-        <v>-8.976691968000008</v>
+        <v>-9.508940480000005</v>
       </c>
       <c r="Q41">
-        <v>4.823308031999993</v>
+        <v>4.291059519999996</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.160518267904176</v>
+        <v>0.1624302390359122</v>
       </c>
       <c r="T41">
-        <v>1.495163601008625</v>
+        <v>1.520082994358769</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1816155671744092</v>
+        <v>0.177075177995049</v>
       </c>
       <c r="W41">
-        <v>0.1643315941113787</v>
+        <v>0.1652433042585942</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5675486474200288</v>
+        <v>0.5533599312345281</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.163555465124985</v>
+        <v>0.165105465124985</v>
       </c>
       <c r="C42">
-        <v>120.3886014227179</v>
+        <v>113.9116052980821</v>
       </c>
       <c r="D42">
-        <v>198.5086014227179</v>
+        <v>195.9296052980821</v>
       </c>
       <c r="E42">
-        <v>144.82</v>
+        <v>148.718</v>
       </c>
       <c r="F42">
-        <v>155.92</v>
+        <v>159.818</v>
       </c>
       <c r="G42">
         <v>77.8</v>
@@ -4731,37 +4731,37 @@
         <v>17.325</v>
       </c>
       <c r="M42">
-        <v>31.308736</v>
+        <v>32.0914544</v>
       </c>
       <c r="N42">
-        <v>-13.98373600000001</v>
+        <v>-14.76645440000001</v>
       </c>
       <c r="O42">
-        <v>-4.474795520000002</v>
+        <v>-4.725265408000003</v>
       </c>
       <c r="P42">
-        <v>-9.508940480000005</v>
+        <v>-10.04118899200001</v>
       </c>
       <c r="Q42">
-        <v>4.291059519999996</v>
+        <v>3.758811007999995</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1624302390359122</v>
+        <v>0.1644070227483853</v>
       </c>
       <c r="T42">
-        <v>1.520082994358769</v>
+        <v>1.545847112907222</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.177075177995049</v>
+        <v>0.1727562712146819</v>
       </c>
       <c r="W42">
-        <v>0.1652433042585942</v>
+        <v>0.1661105407400919</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5533599312345281</v>
+        <v>0.5398633475458811</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.165105465124985</v>
+        <v>0.166655465124985</v>
       </c>
       <c r="C43">
-        <v>113.9116052980821</v>
+        <v>107.500761647214</v>
       </c>
       <c r="D43">
-        <v>195.9296052980821</v>
+        <v>193.416761647214</v>
       </c>
       <c r="E43">
-        <v>148.718</v>
+        <v>152.616</v>
       </c>
       <c r="F43">
-        <v>159.818</v>
+        <v>163.716</v>
       </c>
       <c r="G43">
         <v>77.8</v>
@@ -4813,37 +4813,37 @@
         <v>17.325</v>
       </c>
       <c r="M43">
-        <v>32.0914544</v>
+        <v>32.8741728</v>
       </c>
       <c r="N43">
-        <v>-14.76645440000001</v>
+        <v>-15.54917280000001</v>
       </c>
       <c r="O43">
-        <v>-4.725265408000003</v>
+        <v>-4.975735296000003</v>
       </c>
       <c r="P43">
-        <v>-10.04118899200001</v>
+        <v>-10.573437504</v>
       </c>
       <c r="Q43">
-        <v>3.758811007999995</v>
+        <v>3.226562495999996</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1644070227483853</v>
+        <v>0.166451971416461</v>
       </c>
       <c r="T43">
-        <v>1.545847112907222</v>
+        <v>1.572499649336658</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1727562712146819</v>
+        <v>0.1686430266619514</v>
       </c>
       <c r="W43">
-        <v>0.1661105407400919</v>
+        <v>0.1669364802462802</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5398633475458811</v>
+        <v>0.5270094583185982</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.166655465124985</v>
+        <v>0.168205465124985</v>
       </c>
       <c r="C44">
-        <v>107.500761647214</v>
+        <v>101.1535574368704</v>
       </c>
       <c r="D44">
-        <v>193.416761647214</v>
+        <v>190.9675574368704</v>
       </c>
       <c r="E44">
-        <v>152.616</v>
+        <v>156.514</v>
       </c>
       <c r="F44">
-        <v>163.716</v>
+        <v>167.614</v>
       </c>
       <c r="G44">
         <v>77.8</v>
@@ -4895,37 +4895,37 @@
         <v>17.325</v>
       </c>
       <c r="M44">
-        <v>32.8741728</v>
+        <v>33.6568912</v>
       </c>
       <c r="N44">
-        <v>-15.54917280000001</v>
+        <v>-16.33189120000001</v>
       </c>
       <c r="O44">
-        <v>-4.975735296000003</v>
+        <v>-5.226205184000003</v>
       </c>
       <c r="P44">
-        <v>-10.573437504</v>
+        <v>-11.10568601600001</v>
       </c>
       <c r="Q44">
-        <v>3.226562495999996</v>
+        <v>2.694313983999995</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1664519714164609</v>
+        <v>0.1685686726693813</v>
       </c>
       <c r="T44">
-        <v>1.572499649336657</v>
+        <v>1.600087362482915</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1686430266619514</v>
+        <v>0.1647210958093479</v>
       </c>
       <c r="W44">
-        <v>0.1669364802462802</v>
+        <v>0.167724003961483</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5270094583185982</v>
+        <v>0.5147534244042122</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.168205465124985</v>
+        <v>0.169755465124985</v>
       </c>
       <c r="C45">
-        <v>101.1535574368704</v>
+        <v>94.86760533061442</v>
       </c>
       <c r="D45">
-        <v>190.9675574368704</v>
+        <v>188.5796053306144</v>
       </c>
       <c r="E45">
-        <v>156.514</v>
+        <v>160.412</v>
       </c>
       <c r="F45">
-        <v>167.614</v>
+        <v>171.512</v>
       </c>
       <c r="G45">
         <v>77.8</v>
@@ -4977,37 +4977,37 @@
         <v>17.325</v>
       </c>
       <c r="M45">
-        <v>33.6568912</v>
+        <v>34.4396096</v>
       </c>
       <c r="N45">
-        <v>-16.33189120000001</v>
+        <v>-17.11460960000001</v>
       </c>
       <c r="O45">
-        <v>-5.226205184000003</v>
+        <v>-5.476675072000003</v>
       </c>
       <c r="P45">
-        <v>-11.10568601600001</v>
+        <v>-11.63793452800001</v>
       </c>
       <c r="Q45">
-        <v>2.694313983999995</v>
+        <v>2.162065471999995</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1685686726693813</v>
+        <v>0.1707609703956203</v>
       </c>
       <c r="T45">
-        <v>1.600087362482915</v>
+        <v>1.628660351098681</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1647210958093479</v>
+        <v>0.1609774345409536</v>
       </c>
       <c r="W45">
-        <v>0.167724003961483</v>
+        <v>0.1684757311441765</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5147534244042122</v>
+        <v>0.5030544829404801</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.169755465124985</v>
+        <v>0.187847253629085</v>
       </c>
       <c r="C46">
-        <v>94.86760533061442</v>
+        <v>66.95124349211741</v>
       </c>
       <c r="D46">
-        <v>188.5796053306144</v>
+        <v>164.5612434921174</v>
       </c>
       <c r="E46">
-        <v>160.412</v>
+        <v>164.31</v>
       </c>
       <c r="F46">
-        <v>171.512</v>
+        <v>175.41</v>
       </c>
       <c r="G46">
         <v>77.8</v>
@@ -5059,45 +5059,45 @@
         <v>17.325</v>
       </c>
       <c r="M46">
-        <v>34.4396096</v>
+        <v>41.361678</v>
       </c>
       <c r="N46">
-        <v>-17.11460960000001</v>
+        <v>-24.036678</v>
       </c>
       <c r="O46">
-        <v>-5.476675072000003</v>
+        <v>-7.691736960000001</v>
       </c>
       <c r="P46">
-        <v>-11.63793452800001</v>
+        <v>-16.34494104</v>
       </c>
       <c r="Q46">
-        <v>2.162065471999995</v>
+        <v>-2.544941040000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1707609703956203</v>
+        <v>0.1744726035011769</v>
       </c>
       <c r="T46">
-        <v>1.628660351098681</v>
+        <v>1.67703537297717</v>
       </c>
       <c r="U46">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.1609774345409536</v>
+        <v>0.1340371152253542</v>
       </c>
       <c r="W46">
-        <v>0.1684757311441765</v>
+        <v>0.2041940482298615</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.5030544829404801</v>
+        <v>0.418865985079232</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.187847253629085</v>
+        <v>0.189747253629085</v>
       </c>
       <c r="C47">
-        <v>66.95124349211741</v>
+        <v>60.88115368316076</v>
       </c>
       <c r="D47">
-        <v>164.5612434921174</v>
+        <v>162.3891536831608</v>
       </c>
       <c r="E47">
-        <v>164.31</v>
+        <v>168.208</v>
       </c>
       <c r="F47">
-        <v>175.41</v>
+        <v>179.308</v>
       </c>
       <c r="G47">
         <v>77.8</v>
@@ -5141,37 +5141,37 @@
         <v>17.325</v>
       </c>
       <c r="M47">
-        <v>41.361678</v>
+        <v>42.28082640000001</v>
       </c>
       <c r="N47">
-        <v>-24.036678</v>
+        <v>-24.95582640000001</v>
       </c>
       <c r="O47">
-        <v>-7.691736960000001</v>
+        <v>-7.985864448000005</v>
       </c>
       <c r="P47">
-        <v>-16.34494104</v>
+        <v>-16.96996195200001</v>
       </c>
       <c r="Q47">
-        <v>-2.544941040000001</v>
+        <v>-3.169961952000008</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1744726035011769</v>
+        <v>0.1768554294919395</v>
       </c>
       <c r="T47">
-        <v>1.67703537297717</v>
+        <v>1.708091583587859</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.1340371152253542</v>
+        <v>0.1311232648943682</v>
       </c>
       <c r="W47">
-        <v>0.2041940482298615</v>
+        <v>0.204881134137908</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.418865985079232</v>
+        <v>0.4097602027949007</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.189747253629085</v>
+        <v>0.191647253629085</v>
       </c>
       <c r="C48">
-        <v>60.88115368316076</v>
+        <v>54.86765692665233</v>
       </c>
       <c r="D48">
-        <v>162.3891536831608</v>
+        <v>160.2736569266523</v>
       </c>
       <c r="E48">
-        <v>168.208</v>
+        <v>172.106</v>
       </c>
       <c r="F48">
-        <v>179.308</v>
+        <v>183.206</v>
       </c>
       <c r="G48">
         <v>77.8</v>
@@ -5223,37 +5223,37 @@
         <v>17.325</v>
       </c>
       <c r="M48">
-        <v>42.28082640000001</v>
+        <v>43.19997480000001</v>
       </c>
       <c r="N48">
-        <v>-24.95582640000001</v>
+        <v>-25.87497480000001</v>
       </c>
       <c r="O48">
-        <v>-7.985864448000005</v>
+        <v>-8.279991936000004</v>
       </c>
       <c r="P48">
-        <v>-16.96996195200001</v>
+        <v>-17.59498286400001</v>
       </c>
       <c r="Q48">
-        <v>-3.169961952000008</v>
+        <v>-3.794982864000009</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1768554294919395</v>
+        <v>0.1793281734446176</v>
       </c>
       <c r="T48">
-        <v>1.708091583587859</v>
+        <v>1.740319726674422</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.1311232648943682</v>
+        <v>0.128333408194488</v>
       </c>
       <c r="W48">
-        <v>0.204881134137908</v>
+        <v>0.2055389823477397</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4097602027949007</v>
+        <v>0.4010419006077752</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.191647253629085</v>
+        <v>0.193547253629085</v>
       </c>
       <c r="C49">
-        <v>54.86765692665233</v>
+        <v>48.90856989673617</v>
       </c>
       <c r="D49">
-        <v>160.2736569266523</v>
+        <v>158.2125698967362</v>
       </c>
       <c r="E49">
-        <v>172.106</v>
+        <v>176.004</v>
       </c>
       <c r="F49">
-        <v>183.206</v>
+        <v>187.104</v>
       </c>
       <c r="G49">
         <v>77.8</v>
@@ -5305,37 +5305,37 @@
         <v>17.325</v>
       </c>
       <c r="M49">
-        <v>43.19997480000001</v>
+        <v>44.1191232</v>
       </c>
       <c r="N49">
-        <v>-25.87497480000001</v>
+        <v>-26.79412320000001</v>
       </c>
       <c r="O49">
-        <v>-8.279991936000004</v>
+        <v>-8.574119424000003</v>
       </c>
       <c r="P49">
-        <v>-17.59498286400001</v>
+        <v>-18.22000377600001</v>
       </c>
       <c r="Q49">
-        <v>-3.794982864000009</v>
+        <v>-4.420003776000005</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1793281734446176</v>
+        <v>0.1818960229339371</v>
       </c>
       <c r="T49">
-        <v>1.740319726674422</v>
+        <v>1.773787413725853</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.128333408194488</v>
+        <v>0.1256597955237696</v>
       </c>
       <c r="W49">
-        <v>0.2055389823477397</v>
+        <v>0.2061694202154951</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4010419006077752</v>
+        <v>0.3926868610117799</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.193547253629085</v>
+        <v>0.195447253629085</v>
       </c>
       <c r="C50">
-        <v>48.9085698967362</v>
+        <v>43.00182015015628</v>
       </c>
       <c r="D50">
-        <v>158.2125698967362</v>
+        <v>156.2038201501563</v>
       </c>
       <c r="E50">
-        <v>176.004</v>
+        <v>179.902</v>
       </c>
       <c r="F50">
-        <v>187.104</v>
+        <v>191.002</v>
       </c>
       <c r="G50">
         <v>77.8</v>
@@ -5387,37 +5387,37 @@
         <v>17.325</v>
       </c>
       <c r="M50">
-        <v>44.1191232</v>
+        <v>45.0382716</v>
       </c>
       <c r="N50">
-        <v>-26.7941232</v>
+        <v>-27.71327160000001</v>
       </c>
       <c r="O50">
-        <v>-8.574119424000001</v>
+        <v>-8.868246912000002</v>
       </c>
       <c r="P50">
-        <v>-18.220003776</v>
+        <v>-18.845024688</v>
       </c>
       <c r="Q50">
-        <v>-4.420003775999998</v>
+        <v>-5.045024688000002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1818960229339371</v>
+        <v>0.18456457240323</v>
       </c>
       <c r="T50">
-        <v>1.773787413725853</v>
+        <v>1.808567559093027</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.1256597955237696</v>
+        <v>0.1230953099008355</v>
       </c>
       <c r="W50">
-        <v>0.2061694202154951</v>
+        <v>0.206774125925383</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.39268686101178</v>
+        <v>0.384672843440111</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.195447253629085</v>
+        <v>0.197347253629085</v>
       </c>
       <c r="C51">
-        <v>43.00182015015628</v>
+        <v>37.1454391753899</v>
       </c>
       <c r="D51">
-        <v>156.2038201501563</v>
+        <v>154.2454391753899</v>
       </c>
       <c r="E51">
-        <v>179.902</v>
+        <v>183.8</v>
       </c>
       <c r="F51">
-        <v>191.002</v>
+        <v>194.9</v>
       </c>
       <c r="G51">
         <v>77.8</v>
@@ -5469,37 +5469,37 @@
         <v>17.325</v>
       </c>
       <c r="M51">
-        <v>45.0382716</v>
+        <v>45.95742000000001</v>
       </c>
       <c r="N51">
-        <v>-27.71327160000001</v>
+        <v>-28.63242000000001</v>
       </c>
       <c r="O51">
-        <v>-8.868246912000002</v>
+        <v>-9.162374400000003</v>
       </c>
       <c r="P51">
-        <v>-18.845024688</v>
+        <v>-19.47004560000001</v>
       </c>
       <c r="Q51">
-        <v>-5.045024688000002</v>
+        <v>-5.670045600000005</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.18456457240323</v>
+        <v>0.1873398638512946</v>
       </c>
       <c r="T51">
-        <v>1.808567559093027</v>
+        <v>1.844738910274887</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.1230953099008355</v>
+        <v>0.1206334037028188</v>
       </c>
       <c r="W51">
-        <v>0.206774125925383</v>
+        <v>0.2073546434068753</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.384672843440111</v>
+        <v>0.3769793865713087</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.197347253629085</v>
+        <v>0.199247253629085</v>
       </c>
       <c r="C52">
-        <v>37.1454391753899</v>
+        <v>31.33755595817934</v>
       </c>
       <c r="D52">
-        <v>154.2454391753899</v>
+        <v>152.3355559581794</v>
       </c>
       <c r="E52">
-        <v>183.8</v>
+        <v>187.698</v>
       </c>
       <c r="F52">
-        <v>194.9</v>
+        <v>198.798</v>
       </c>
       <c r="G52">
         <v>77.8</v>
@@ -5551,37 +5551,37 @@
         <v>17.325</v>
       </c>
       <c r="M52">
-        <v>45.95742000000001</v>
+        <v>46.8765684</v>
       </c>
       <c r="N52">
-        <v>-28.63242000000001</v>
+        <v>-29.55156840000001</v>
       </c>
       <c r="O52">
-        <v>-9.162374400000003</v>
+        <v>-9.456501888000004</v>
       </c>
       <c r="P52">
-        <v>-19.47004560000001</v>
+        <v>-20.095066512</v>
       </c>
       <c r="Q52">
-        <v>-5.670045600000005</v>
+        <v>-6.295066512000002</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1873398638512946</v>
+        <v>0.190228432501321</v>
       </c>
       <c r="T52">
-        <v>1.844738910274887</v>
+        <v>1.88238664313764</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.1206334037028188</v>
+        <v>0.1182680428459008</v>
       </c>
       <c r="W52">
-        <v>0.2073546434068753</v>
+        <v>0.2079123954969366</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3769793865713087</v>
+        <v>0.36958763389344</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.199247253629085</v>
+        <v>0.201147253629085</v>
       </c>
       <c r="C53">
-        <v>31.33755595817934</v>
+        <v>25.57639101925088</v>
       </c>
       <c r="D53">
-        <v>152.3355559581794</v>
+        <v>150.4723910192509</v>
       </c>
       <c r="E53">
-        <v>187.698</v>
+        <v>191.596</v>
       </c>
       <c r="F53">
-        <v>198.798</v>
+        <v>202.696</v>
       </c>
       <c r="G53">
         <v>77.8</v>
@@ -5633,37 +5633,37 @@
         <v>17.325</v>
       </c>
       <c r="M53">
-        <v>46.8765684</v>
+        <v>47.79571680000001</v>
       </c>
       <c r="N53">
-        <v>-29.55156840000001</v>
+        <v>-30.47071680000001</v>
       </c>
       <c r="O53">
-        <v>-9.456501888000004</v>
+        <v>-9.750629376000004</v>
       </c>
       <c r="P53">
-        <v>-20.095066512</v>
+        <v>-20.72008742400001</v>
       </c>
       <c r="Q53">
-        <v>-6.295066512000002</v>
+        <v>-6.920087424000005</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.190228432501321</v>
+        <v>0.1932373581784319</v>
       </c>
       <c r="T53">
-        <v>1.88238664313764</v>
+        <v>1.921603031536341</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.1182680428459008</v>
+        <v>0.1159936574065565</v>
       </c>
       <c r="W53">
-        <v>0.2079123954969366</v>
+        <v>0.208448695583534</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.36958763389344</v>
+        <v>0.3624801793954892</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.201147253629085</v>
+        <v>0.203047253629085</v>
       </c>
       <c r="C54">
-        <v>25.57639101925088</v>
+        <v>19.86025088428252</v>
       </c>
       <c r="D54">
-        <v>150.4723910192509</v>
+        <v>148.6542508842826</v>
       </c>
       <c r="E54">
-        <v>191.596</v>
+        <v>195.494</v>
       </c>
       <c r="F54">
-        <v>202.696</v>
+        <v>206.594</v>
       </c>
       <c r="G54">
         <v>77.8</v>
@@ -5715,37 +5715,37 @@
         <v>17.325</v>
       </c>
       <c r="M54">
-        <v>47.79571680000001</v>
+        <v>48.71486520000001</v>
       </c>
       <c r="N54">
-        <v>-30.47071680000001</v>
+        <v>-31.38986520000001</v>
       </c>
       <c r="O54">
-        <v>-9.750629376000004</v>
+        <v>-10.044756864</v>
       </c>
       <c r="P54">
-        <v>-20.72008742400001</v>
+        <v>-21.34510833600001</v>
       </c>
       <c r="Q54">
-        <v>-6.920087424000005</v>
+        <v>-7.545108336000006</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1932373581784319</v>
+        <v>0.1963743232460581</v>
       </c>
       <c r="T54">
-        <v>1.921603031536341</v>
+        <v>1.962488202420093</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.1159936574065565</v>
+        <v>0.1138050978328479</v>
       </c>
       <c r="W54">
-        <v>0.208448695583534</v>
+        <v>0.2089647579310145</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3624801793954892</v>
+        <v>0.3556409307276497</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.203047253629085</v>
+        <v>0.204947253629085</v>
       </c>
       <c r="C55">
-        <v>19.86025088428252</v>
+        <v>14.18752294999842</v>
       </c>
       <c r="D55">
-        <v>148.6542508842826</v>
+        <v>146.8795229499985</v>
       </c>
       <c r="E55">
-        <v>195.494</v>
+        <v>199.392</v>
       </c>
       <c r="F55">
-        <v>206.594</v>
+        <v>210.492</v>
       </c>
       <c r="G55">
         <v>77.8</v>
@@ -5797,37 +5797,37 @@
         <v>17.325</v>
       </c>
       <c r="M55">
-        <v>48.71486520000001</v>
+        <v>49.6340136</v>
       </c>
       <c r="N55">
-        <v>-31.38986520000001</v>
+        <v>-32.30901360000001</v>
       </c>
       <c r="O55">
-        <v>-10.044756864</v>
+        <v>-10.338884352</v>
       </c>
       <c r="P55">
-        <v>-21.34510833600001</v>
+        <v>-21.97012924800001</v>
       </c>
       <c r="Q55">
-        <v>-7.545108336000006</v>
+        <v>-8.170129248000006</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1963743232460581</v>
+        <v>0.1996476780992333</v>
       </c>
       <c r="T55">
-        <v>1.962488202420093</v>
+        <v>2.005150989429225</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.1138050978328479</v>
+        <v>0.1116975960211285</v>
       </c>
       <c r="W55">
-        <v>0.2089647579310145</v>
+        <v>0.2094617068582179</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3556409307276497</v>
+        <v>0.3490549875660266</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.204947253629085</v>
+        <v>0.206847253629085</v>
       </c>
       <c r="C56">
-        <v>14.18752294999842</v>
+        <v>8.556670713674436</v>
       </c>
       <c r="D56">
-        <v>146.8795229499985</v>
+        <v>145.1466707136745</v>
       </c>
       <c r="E56">
-        <v>199.392</v>
+        <v>203.29</v>
       </c>
       <c r="F56">
-        <v>210.492</v>
+        <v>214.39</v>
       </c>
       <c r="G56">
         <v>77.8</v>
@@ -5879,37 +5879,37 @@
         <v>17.325</v>
       </c>
       <c r="M56">
-        <v>49.6340136</v>
+        <v>50.55316200000001</v>
       </c>
       <c r="N56">
-        <v>-32.30901360000001</v>
+        <v>-33.22816200000001</v>
       </c>
       <c r="O56">
-        <v>-10.338884352</v>
+        <v>-10.63301184</v>
       </c>
       <c r="P56">
-        <v>-21.97012924800001</v>
+        <v>-22.59515016000001</v>
       </c>
       <c r="Q56">
-        <v>-8.170129248000006</v>
+        <v>-8.795150160000009</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1996476780992333</v>
+        <v>0.2030665153903274</v>
       </c>
       <c r="T56">
-        <v>2.005150989429225</v>
+        <v>2.049709900305431</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.1116975960211285</v>
+        <v>0.1096667306389262</v>
       </c>
       <c r="W56">
-        <v>0.2094617068582179</v>
+        <v>0.2099405849153412</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3490549875660266</v>
+        <v>0.3427085332466443</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.206847253629085</v>
+        <v>0.208747253629085</v>
       </c>
       <c r="C57">
-        <v>8.556670713674436</v>
+        <v>2.966229336394548</v>
       </c>
       <c r="D57">
-        <v>145.1466707136745</v>
+        <v>143.4542293363946</v>
       </c>
       <c r="E57">
-        <v>203.29</v>
+        <v>207.188</v>
       </c>
       <c r="F57">
-        <v>214.39</v>
+        <v>218.288</v>
       </c>
       <c r="G57">
         <v>77.8</v>
@@ -5961,37 +5961,37 @@
         <v>17.325</v>
       </c>
       <c r="M57">
-        <v>50.55316200000001</v>
+        <v>51.47231040000001</v>
       </c>
       <c r="N57">
-        <v>-33.22816200000001</v>
+        <v>-34.14731040000002</v>
       </c>
       <c r="O57">
-        <v>-10.63301184</v>
+        <v>-10.92713932800001</v>
       </c>
       <c r="P57">
-        <v>-22.59515016000001</v>
+        <v>-23.22017107200001</v>
       </c>
       <c r="Q57">
-        <v>-8.795150160000009</v>
+        <v>-9.420171072000009</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2030665153903274</v>
+        <v>0.2066407543764712</v>
       </c>
       <c r="T57">
-        <v>2.049709900305431</v>
+        <v>2.096294216221463</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.1096667306389262</v>
+        <v>0.1077083961632311</v>
       </c>
       <c r="W57">
-        <v>0.2099405849153412</v>
+        <v>0.2104023601847101</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3427085332466443</v>
+        <v>0.336588738010097</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.208747253629085</v>
+        <v>0.210647253629085</v>
       </c>
       <c r="C58">
-        <v>2.966229336394548</v>
+        <v>-2.585198486870468</v>
       </c>
       <c r="D58">
-        <v>143.4542293363946</v>
+        <v>141.8008015131296</v>
       </c>
       <c r="E58">
-        <v>207.188</v>
+        <v>211.086</v>
       </c>
       <c r="F58">
-        <v>218.288</v>
+        <v>222.186</v>
       </c>
       <c r="G58">
         <v>77.8</v>
@@ -6043,37 +6043,37 @@
         <v>17.325</v>
       </c>
       <c r="M58">
-        <v>51.47231040000001</v>
+        <v>52.39145880000001</v>
       </c>
       <c r="N58">
-        <v>-34.14731040000002</v>
+        <v>-35.06645880000001</v>
       </c>
       <c r="O58">
-        <v>-10.92713932800001</v>
+        <v>-11.22126681600001</v>
       </c>
       <c r="P58">
-        <v>-23.22017107200001</v>
+        <v>-23.84519198400001</v>
       </c>
       <c r="Q58">
-        <v>-9.420171072000009</v>
+        <v>-10.04519198400001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2066407543764712</v>
+        <v>0.2103812370363891</v>
       </c>
       <c r="T58">
-        <v>2.096294216221463</v>
+        <v>2.145045244505684</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.1077083961632311</v>
+        <v>0.1058187751779112</v>
       </c>
       <c r="W58">
-        <v>0.2104023601847101</v>
+        <v>0.2108479328130486</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.336588738010097</v>
+        <v>0.3306836724309725</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.210647253629085</v>
+        <v>0.212547253629085</v>
       </c>
       <c r="C59">
-        <v>-2.585198486870468</v>
+        <v>-8.098946374834185</v>
       </c>
       <c r="D59">
-        <v>141.8008015131296</v>
+        <v>140.1850536251659</v>
       </c>
       <c r="E59">
-        <v>211.086</v>
+        <v>214.984</v>
       </c>
       <c r="F59">
-        <v>222.186</v>
+        <v>226.084</v>
       </c>
       <c r="G59">
         <v>77.8</v>
@@ -6125,37 +6125,37 @@
         <v>17.325</v>
       </c>
       <c r="M59">
-        <v>52.39145880000001</v>
+        <v>53.31060720000001</v>
       </c>
       <c r="N59">
-        <v>-35.06645880000001</v>
+        <v>-35.98560720000001</v>
       </c>
       <c r="O59">
-        <v>-11.22126681600001</v>
+        <v>-11.515394304</v>
       </c>
       <c r="P59">
-        <v>-23.84519198400001</v>
+        <v>-24.47021289600001</v>
       </c>
       <c r="Q59">
-        <v>-10.04519198400001</v>
+        <v>-10.67021289600001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2103812370363891</v>
+        <v>0.2142998379182079</v>
       </c>
       <c r="T59">
-        <v>2.145045244505684</v>
+        <v>2.196117750327247</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.1058187751779112</v>
+        <v>0.1039943135369127</v>
       </c>
       <c r="W59">
-        <v>0.2108479328130486</v>
+        <v>0.211278140867996</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3306836724309725</v>
+        <v>0.3249822298028523</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.212547253629085</v>
+        <v>0.214447253629085</v>
       </c>
       <c r="C60">
-        <v>-8.0989463748341</v>
+        <v>-13.57628784738259</v>
       </c>
       <c r="D60">
-        <v>140.1850536251659</v>
+        <v>138.6057121526174</v>
       </c>
       <c r="E60">
-        <v>214.984</v>
+        <v>218.882</v>
       </c>
       <c r="F60">
-        <v>226.084</v>
+        <v>229.982</v>
       </c>
       <c r="G60">
         <v>77.8</v>
@@ -6207,37 +6207,37 @@
         <v>17.325</v>
       </c>
       <c r="M60">
-        <v>53.3106072</v>
+        <v>54.2297556</v>
       </c>
       <c r="N60">
-        <v>-35.9856072</v>
+        <v>-36.90475560000001</v>
       </c>
       <c r="O60">
-        <v>-11.515394304</v>
+        <v>-11.809521792</v>
       </c>
       <c r="P60">
-        <v>-24.470212896</v>
+        <v>-25.095233808</v>
       </c>
       <c r="Q60">
-        <v>-10.670212896</v>
+        <v>-11.295233808</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2142998379182079</v>
+        <v>0.2184095900625544</v>
       </c>
       <c r="T60">
-        <v>2.196117750327247</v>
+        <v>2.249681597896204</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.1039943135369128</v>
+        <v>0.1022316980532363</v>
       </c>
       <c r="W60">
-        <v>0.211278140867996</v>
+        <v>0.2116937655990469</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3249822298028524</v>
+        <v>0.3194740564163633</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.214447253629085</v>
+        <v>0.216347253629085</v>
       </c>
       <c r="C61">
-        <v>-13.57628784738259</v>
+        <v>-19.01843967326141</v>
       </c>
       <c r="D61">
-        <v>138.6057121526174</v>
+        <v>137.0615603267386</v>
       </c>
       <c r="E61">
-        <v>218.882</v>
+        <v>222.78</v>
       </c>
       <c r="F61">
-        <v>229.982</v>
+        <v>233.88</v>
       </c>
       <c r="G61">
         <v>77.8</v>
@@ -6289,37 +6289,37 @@
         <v>17.325</v>
       </c>
       <c r="M61">
-        <v>54.2297556</v>
+        <v>55.148904</v>
       </c>
       <c r="N61">
-        <v>-36.90475560000001</v>
+        <v>-37.82390400000001</v>
       </c>
       <c r="O61">
-        <v>-11.809521792</v>
+        <v>-12.10364928</v>
       </c>
       <c r="P61">
-        <v>-25.095233808</v>
+        <v>-25.72025472</v>
       </c>
       <c r="Q61">
-        <v>-11.295233808</v>
+        <v>-11.92025472</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2184095900625544</v>
+        <v>0.2227248298141183</v>
       </c>
       <c r="T61">
-        <v>2.249681597896204</v>
+        <v>2.305923637843609</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1022316980532363</v>
+        <v>0.1005278364190157</v>
       </c>
       <c r="W61">
-        <v>0.2116937655990469</v>
+        <v>0.2120955361723961</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3194740564163633</v>
+        <v>0.3141494888094239</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.216347253629085</v>
+        <v>0.218247253629085</v>
       </c>
       <c r="C62">
-        <v>-19.01843967326141</v>
+        <v>-24.42656499645696</v>
       </c>
       <c r="D62">
-        <v>137.0615603267386</v>
+        <v>135.551435003543</v>
       </c>
       <c r="E62">
-        <v>222.78</v>
+        <v>226.678</v>
       </c>
       <c r="F62">
-        <v>233.88</v>
+        <v>237.778</v>
       </c>
       <c r="G62">
         <v>77.8</v>
@@ -6371,37 +6371,37 @@
         <v>17.325</v>
       </c>
       <c r="M62">
-        <v>55.148904</v>
+        <v>56.0680524</v>
       </c>
       <c r="N62">
-        <v>-37.82390400000001</v>
+        <v>-38.7430524</v>
       </c>
       <c r="O62">
-        <v>-12.10364928</v>
+        <v>-12.397776768</v>
       </c>
       <c r="P62">
-        <v>-25.72025472</v>
+        <v>-26.345275632</v>
       </c>
       <c r="Q62">
-        <v>-11.92025472</v>
+        <v>-12.545275632</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2227248298141183</v>
+        <v>0.2272613639119162</v>
       </c>
       <c r="T62">
-        <v>2.305923637843609</v>
+        <v>2.365049884967805</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1005278364190157</v>
+        <v>0.09887983910067115</v>
       </c>
       <c r="W62">
-        <v>0.2120955361723961</v>
+        <v>0.2124841339400618</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3141494888094239</v>
+        <v>0.3089994971895973</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.218247253629085</v>
+        <v>0.220147253629085</v>
       </c>
       <c r="C63">
-        <v>-24.42656499645696</v>
+        <v>-29.80177625815341</v>
       </c>
       <c r="D63">
-        <v>135.551435003543</v>
+        <v>134.0742237418466</v>
       </c>
       <c r="E63">
-        <v>226.678</v>
+        <v>230.576</v>
       </c>
       <c r="F63">
-        <v>237.778</v>
+        <v>241.676</v>
       </c>
       <c r="G63">
         <v>77.8</v>
@@ -6453,37 +6453,37 @@
         <v>17.325</v>
       </c>
       <c r="M63">
-        <v>56.0680524</v>
+        <v>56.9872008</v>
       </c>
       <c r="N63">
-        <v>-38.7430524</v>
+        <v>-39.66220080000001</v>
       </c>
       <c r="O63">
-        <v>-12.397776768</v>
+        <v>-12.691904256</v>
       </c>
       <c r="P63">
-        <v>-26.345275632</v>
+        <v>-26.97029654400001</v>
       </c>
       <c r="Q63">
-        <v>-12.545275632</v>
+        <v>-13.17029654400001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2272613639119162</v>
+        <v>0.2320366629622297</v>
       </c>
       <c r="T63">
-        <v>2.365049884967805</v>
+        <v>2.427288039835378</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.09887983910067115</v>
+        <v>0.09728500298614419</v>
       </c>
       <c r="W63">
-        <v>0.2124841339400618</v>
+        <v>0.2128601962958672</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3089994971895973</v>
+        <v>0.3040156343317005</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.220147253629085</v>
+        <v>0.222047253629085</v>
       </c>
       <c r="C64">
-        <v>-29.80177625815341</v>
+        <v>-35.14513792969251</v>
       </c>
       <c r="D64">
-        <v>134.0742237418466</v>
+        <v>132.6288620703075</v>
       </c>
       <c r="E64">
-        <v>230.576</v>
+        <v>234.474</v>
       </c>
       <c r="F64">
-        <v>241.676</v>
+        <v>245.574</v>
       </c>
       <c r="G64">
         <v>77.8</v>
@@ -6535,37 +6535,37 @@
         <v>17.325</v>
       </c>
       <c r="M64">
-        <v>56.9872008</v>
+        <v>57.90634920000001</v>
       </c>
       <c r="N64">
-        <v>-39.66220080000001</v>
+        <v>-40.58134920000001</v>
       </c>
       <c r="O64">
-        <v>-12.691904256</v>
+        <v>-12.986031744</v>
       </c>
       <c r="P64">
-        <v>-26.97029654400001</v>
+        <v>-27.59531745600001</v>
       </c>
       <c r="Q64">
-        <v>-13.17029654400001</v>
+        <v>-13.79531745600001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2320366629622297</v>
+        <v>0.2370700862855332</v>
       </c>
       <c r="T64">
-        <v>2.427288039835378</v>
+        <v>2.492890419290388</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.09728500298614419</v>
+        <v>0.09574079658953873</v>
       </c>
       <c r="W64">
-        <v>0.2128601962958672</v>
+        <v>0.2132243201641868</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3040156343317005</v>
+        <v>0.2991899893423084</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.222047253629085</v>
+        <v>0.223947253629085</v>
       </c>
       <c r="C65">
-        <v>-35.14513792969251</v>
+        <v>-40.45766907064544</v>
       </c>
       <c r="D65">
-        <v>132.6288620703075</v>
+        <v>131.2143309293546</v>
       </c>
       <c r="E65">
-        <v>234.474</v>
+        <v>238.372</v>
       </c>
       <c r="F65">
-        <v>245.574</v>
+        <v>249.472</v>
       </c>
       <c r="G65">
         <v>77.8</v>
@@ -6617,37 +6617,37 @@
         <v>17.325</v>
       </c>
       <c r="M65">
-        <v>57.90634920000001</v>
+        <v>58.82549760000001</v>
       </c>
       <c r="N65">
-        <v>-40.58134920000001</v>
+        <v>-41.50049760000001</v>
       </c>
       <c r="O65">
-        <v>-12.986031744</v>
+        <v>-13.280159232</v>
       </c>
       <c r="P65">
-        <v>-27.59531745600001</v>
+        <v>-28.22033836800001</v>
       </c>
       <c r="Q65">
-        <v>-13.79531745600001</v>
+        <v>-14.42033836800001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2370700862855332</v>
+        <v>0.2423831442379092</v>
       </c>
       <c r="T65">
-        <v>2.492890419290388</v>
+        <v>2.562137375381788</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.09574079658953873</v>
+        <v>0.09424484664282717</v>
       </c>
       <c r="W65">
-        <v>0.2132243201641868</v>
+        <v>0.2135770651616214</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2991899893423084</v>
+        <v>0.294515145758835</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.223947253629085</v>
+        <v>0.225847253629085</v>
       </c>
       <c r="C66">
-        <v>-40.45766907064544</v>
+        <v>-45.74034572491632</v>
       </c>
       <c r="D66">
-        <v>131.2143309293546</v>
+        <v>129.8296542750837</v>
       </c>
       <c r="E66">
-        <v>238.372</v>
+        <v>242.27</v>
       </c>
       <c r="F66">
-        <v>249.472</v>
+        <v>253.37</v>
       </c>
       <c r="G66">
         <v>77.8</v>
@@ -6699,37 +6699,37 @@
         <v>17.325</v>
       </c>
       <c r="M66">
-        <v>58.82549760000001</v>
+        <v>59.744646</v>
       </c>
       <c r="N66">
-        <v>-41.50049760000001</v>
+        <v>-42.41964600000001</v>
       </c>
       <c r="O66">
-        <v>-13.280159232</v>
+        <v>-13.57428672</v>
       </c>
       <c r="P66">
-        <v>-28.22033836800001</v>
+        <v>-28.84535928</v>
       </c>
       <c r="Q66">
-        <v>-14.42033836800001</v>
+        <v>-15.04535928</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2423831442379092</v>
+        <v>0.2479998055018495</v>
       </c>
       <c r="T66">
-        <v>2.562137375381788</v>
+        <v>2.635341300392696</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.09424484664282717</v>
+        <v>0.09279492592524523</v>
       </c>
       <c r="W66">
-        <v>0.2135770651616214</v>
+        <v>0.2139189564668272</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.294515145758835</v>
+        <v>0.2899841435163913</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.225847253629085</v>
+        <v>0.227747253629085</v>
       </c>
       <c r="C67">
-        <v>-45.74034572491632</v>
+        <v>-50.99410316671606</v>
       </c>
       <c r="D67">
-        <v>129.8296542750837</v>
+        <v>128.473896833284</v>
       </c>
       <c r="E67">
-        <v>242.27</v>
+        <v>246.168</v>
       </c>
       <c r="F67">
-        <v>253.37</v>
+        <v>257.268</v>
       </c>
       <c r="G67">
         <v>77.8</v>
@@ -6781,37 +6781,37 @@
         <v>17.325</v>
       </c>
       <c r="M67">
-        <v>59.744646</v>
+        <v>60.66379440000001</v>
       </c>
       <c r="N67">
-        <v>-42.41964600000001</v>
+        <v>-43.33879440000001</v>
       </c>
       <c r="O67">
-        <v>-13.57428672</v>
+        <v>-13.868414208</v>
       </c>
       <c r="P67">
-        <v>-28.84535928</v>
+        <v>-29.47038019200001</v>
       </c>
       <c r="Q67">
-        <v>-15.04535928</v>
+        <v>-15.67038019200001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2479998055018495</v>
+        <v>0.253946858604845</v>
       </c>
       <c r="T67">
-        <v>2.635341300392696</v>
+        <v>2.71285133863954</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09279492592524523</v>
+        <v>0.09138894219910514</v>
       </c>
       <c r="W67">
-        <v>0.2139189564668272</v>
+        <v>0.214250487429451</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2899841435163913</v>
+        <v>0.2855904443722036</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.227747253629085</v>
+        <v>0.229647253629085</v>
       </c>
       <c r="C68">
-        <v>-50.99410316671606</v>
+        <v>-56.21983800726861</v>
       </c>
       <c r="D68">
-        <v>128.473896833284</v>
+        <v>127.1461619927314</v>
       </c>
       <c r="E68">
-        <v>246.168</v>
+        <v>250.066</v>
       </c>
       <c r="F68">
-        <v>257.268</v>
+        <v>261.166</v>
       </c>
       <c r="G68">
         <v>77.8</v>
@@ -6863,37 +6863,37 @@
         <v>17.325</v>
       </c>
       <c r="M68">
-        <v>60.66379440000001</v>
+        <v>61.5829428</v>
       </c>
       <c r="N68">
-        <v>-43.33879440000001</v>
+        <v>-44.25794280000001</v>
       </c>
       <c r="O68">
-        <v>-13.868414208</v>
+        <v>-14.162541696</v>
       </c>
       <c r="P68">
-        <v>-29.47038019200001</v>
+        <v>-30.095401104</v>
       </c>
       <c r="Q68">
-        <v>-15.67038019200001</v>
+        <v>-16.295401104</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.253946858604845</v>
+        <v>0.2602543391686282</v>
       </c>
       <c r="T68">
-        <v>2.71285133863954</v>
+        <v>2.795058954961951</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09138894219910514</v>
+        <v>0.09002492813643194</v>
       </c>
       <c r="W68">
-        <v>0.214250487429451</v>
+        <v>0.2145721219454294</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2855904443722036</v>
+        <v>0.2813279004263498</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.229647253629085</v>
+        <v>0.231547253629085</v>
       </c>
       <c r="C69">
-        <v>-56.21983800726861</v>
+        <v>-61.41841017222021</v>
       </c>
       <c r="D69">
-        <v>127.1461619927314</v>
+        <v>125.8455898277798</v>
       </c>
       <c r="E69">
-        <v>250.066</v>
+        <v>253.964</v>
       </c>
       <c r="F69">
-        <v>261.166</v>
+        <v>265.064</v>
       </c>
       <c r="G69">
         <v>77.8</v>
@@ -6945,37 +6945,37 @@
         <v>17.325</v>
       </c>
       <c r="M69">
-        <v>61.5829428</v>
+        <v>62.50209120000001</v>
       </c>
       <c r="N69">
-        <v>-44.25794280000001</v>
+        <v>-45.17709120000001</v>
       </c>
       <c r="O69">
-        <v>-14.162541696</v>
+        <v>-14.456669184</v>
       </c>
       <c r="P69">
-        <v>-30.095401104</v>
+        <v>-30.72042201600001</v>
       </c>
       <c r="Q69">
-        <v>-16.295401104</v>
+        <v>-16.92042201600001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2602543391686282</v>
+        <v>0.2669560372676479</v>
       </c>
       <c r="T69">
-        <v>2.795058954961951</v>
+        <v>2.882404547304512</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09002492813643194</v>
+        <v>0.08870103213442557</v>
       </c>
       <c r="W69">
-        <v>0.2145721219454294</v>
+        <v>0.2148842966227024</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2813279004263498</v>
+        <v>0.2771907254200799</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.231547253629085</v>
+        <v>0.233447253629085</v>
       </c>
       <c r="C70">
-        <v>-61.41841017222021</v>
+        <v>-66.59064475891668</v>
       </c>
       <c r="D70">
-        <v>125.8455898277798</v>
+        <v>124.5713552410834</v>
       </c>
       <c r="E70">
-        <v>253.964</v>
+        <v>257.862</v>
       </c>
       <c r="F70">
-        <v>265.064</v>
+        <v>268.962</v>
       </c>
       <c r="G70">
         <v>77.8</v>
@@ -7027,37 +7027,37 @@
         <v>17.325</v>
       </c>
       <c r="M70">
-        <v>62.50209120000001</v>
+        <v>63.42123960000001</v>
       </c>
       <c r="N70">
-        <v>-45.17709120000001</v>
+        <v>-46.09623960000002</v>
       </c>
       <c r="O70">
-        <v>-14.456669184</v>
+        <v>-14.75079667200001</v>
       </c>
       <c r="P70">
-        <v>-30.72042201600001</v>
+        <v>-31.34544292800001</v>
       </c>
       <c r="Q70">
-        <v>-16.92042201600001</v>
+        <v>-17.54544292800001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2669560372676479</v>
+        <v>0.274090102985959</v>
       </c>
       <c r="T70">
-        <v>2.882404547304512</v>
+        <v>2.975385339153044</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.08870103213442557</v>
+        <v>0.08741550992957882</v>
       </c>
       <c r="W70">
-        <v>0.2148842966227024</v>
+        <v>0.2151874227586053</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2771907254200799</v>
+        <v>0.2731734685299338</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.233447253629085</v>
+        <v>0.235347253629085</v>
       </c>
       <c r="C71">
-        <v>-66.59064475891668</v>
+        <v>-71.73733378197798</v>
       </c>
       <c r="D71">
-        <v>124.5713552410834</v>
+        <v>123.322666218022</v>
       </c>
       <c r="E71">
-        <v>257.862</v>
+        <v>261.76</v>
       </c>
       <c r="F71">
-        <v>268.962</v>
+        <v>272.86</v>
       </c>
       <c r="G71">
         <v>77.8</v>
@@ -7109,37 +7109,37 @@
         <v>17.325</v>
       </c>
       <c r="M71">
-        <v>63.42123960000001</v>
+        <v>64.340388</v>
       </c>
       <c r="N71">
-        <v>-46.09623960000002</v>
+        <v>-47.01538800000001</v>
       </c>
       <c r="O71">
-        <v>-14.75079667200001</v>
+        <v>-15.04492416</v>
       </c>
       <c r="P71">
-        <v>-31.34544292800001</v>
+        <v>-31.97046384000001</v>
       </c>
       <c r="Q71">
-        <v>-17.54544292800001</v>
+        <v>-18.17046384000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.274090102985959</v>
+        <v>0.281699773085491</v>
       </c>
       <c r="T71">
-        <v>2.975385339153044</v>
+        <v>3.074564850458146</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.08741550992957882</v>
+        <v>0.08616671693058485</v>
       </c>
       <c r="W71">
-        <v>0.2151874227586053</v>
+        <v>0.2154818881477681</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2731734685299338</v>
+        <v>0.2692709904080777</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.235347253629085</v>
+        <v>0.237247253629085</v>
       </c>
       <c r="C72">
-        <v>-71.73733378197798</v>
+        <v>-76.85923781493011</v>
       </c>
       <c r="D72">
-        <v>123.322666218022</v>
+        <v>122.0987621850699</v>
       </c>
       <c r="E72">
-        <v>261.76</v>
+        <v>265.658</v>
       </c>
       <c r="F72">
-        <v>272.86</v>
+        <v>276.758</v>
       </c>
       <c r="G72">
         <v>77.8</v>
@@ -7191,37 +7191,37 @@
         <v>17.325</v>
       </c>
       <c r="M72">
-        <v>64.340388</v>
+        <v>65.25953640000002</v>
       </c>
       <c r="N72">
-        <v>-47.01538800000001</v>
+        <v>-47.93453640000002</v>
       </c>
       <c r="O72">
-        <v>-15.04492416</v>
+        <v>-15.33905164800001</v>
       </c>
       <c r="P72">
-        <v>-31.97046384000001</v>
+        <v>-32.59548475200001</v>
       </c>
       <c r="Q72">
-        <v>-18.17046384000001</v>
+        <v>-18.79548475200001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.281699773085491</v>
+        <v>0.2898342480194735</v>
       </c>
       <c r="T72">
-        <v>3.074564850458146</v>
+        <v>3.180584328060152</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.08616671693058485</v>
+        <v>0.08495310119916814</v>
       </c>
       <c r="W72">
-        <v>0.2154818881477681</v>
+        <v>0.2157680587372362</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2692709904080777</v>
+        <v>0.2654784412474005</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.237247253629085</v>
+        <v>0.239147253629085</v>
       </c>
       <c r="C73">
-        <v>-76.85923781493005</v>
+        <v>-81.95708753504391</v>
       </c>
       <c r="D73">
-        <v>122.0987621850699</v>
+        <v>120.8989124649561</v>
       </c>
       <c r="E73">
-        <v>265.658</v>
+        <v>269.556</v>
       </c>
       <c r="F73">
-        <v>276.758</v>
+        <v>280.656</v>
       </c>
       <c r="G73">
         <v>77.8</v>
@@ -7273,37 +7273,37 @@
         <v>17.325</v>
       </c>
       <c r="M73">
-        <v>65.2595364</v>
+        <v>66.1786848</v>
       </c>
       <c r="N73">
-        <v>-47.93453640000001</v>
+        <v>-48.8536848</v>
       </c>
       <c r="O73">
-        <v>-15.339051648</v>
+        <v>-15.633179136</v>
       </c>
       <c r="P73">
-        <v>-32.595484752</v>
+        <v>-33.220505664</v>
       </c>
       <c r="Q73">
-        <v>-18.795484752</v>
+        <v>-19.420505664</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2898342480194734</v>
+        <v>0.2985497568773118</v>
       </c>
       <c r="T73">
-        <v>3.18058432806015</v>
+        <v>3.29417662549087</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08495310119916816</v>
+        <v>0.08377319701584639</v>
       </c>
       <c r="W73">
-        <v>0.2157680587372361</v>
+        <v>0.2160462801436634</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2654784412474005</v>
+        <v>0.26179124067452</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.239147253629085</v>
+        <v>0.241047253629085</v>
       </c>
       <c r="C74">
-        <v>-81.95708753504391</v>
+        <v>-87.0315851779751</v>
       </c>
       <c r="D74">
-        <v>120.8989124649561</v>
+        <v>119.7224148220249</v>
       </c>
       <c r="E74">
-        <v>269.556</v>
+        <v>273.454</v>
       </c>
       <c r="F74">
-        <v>280.656</v>
+        <v>284.554</v>
       </c>
       <c r="G74">
         <v>77.8</v>
@@ -7355,37 +7355,37 @@
         <v>17.325</v>
       </c>
       <c r="M74">
-        <v>66.1786848</v>
+        <v>67.0978332</v>
       </c>
       <c r="N74">
-        <v>-48.8536848</v>
+        <v>-49.7728332</v>
       </c>
       <c r="O74">
-        <v>-15.633179136</v>
+        <v>-15.927306624</v>
       </c>
       <c r="P74">
-        <v>-33.220505664</v>
+        <v>-33.845526576</v>
       </c>
       <c r="Q74">
-        <v>-19.420505664</v>
+        <v>-20.045526576</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2985497568773118</v>
+        <v>0.3079108589838789</v>
       </c>
       <c r="T74">
-        <v>3.29417662549087</v>
+        <v>3.416183167175717</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08377319701584639</v>
+        <v>0.08262561897453344</v>
       </c>
       <c r="W74">
-        <v>0.2160462801436634</v>
+        <v>0.216316879045805</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.26179124067452</v>
+        <v>0.2582050592954169</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.241047253629085</v>
+        <v>0.242947253629085</v>
       </c>
       <c r="C75">
-        <v>-87.0315851779751</v>
+        <v>-92.08340590828982</v>
       </c>
       <c r="D75">
-        <v>119.7224148220249</v>
+        <v>118.5685940917102</v>
       </c>
       <c r="E75">
-        <v>273.454</v>
+        <v>277.352</v>
       </c>
       <c r="F75">
-        <v>284.554</v>
+        <v>288.452</v>
       </c>
       <c r="G75">
         <v>77.8</v>
@@ -7437,37 +7437,37 @@
         <v>17.325</v>
       </c>
       <c r="M75">
-        <v>67.0978332</v>
+        <v>68.01698160000001</v>
       </c>
       <c r="N75">
-        <v>-49.7728332</v>
+        <v>-50.69198160000001</v>
       </c>
       <c r="O75">
-        <v>-15.927306624</v>
+        <v>-16.221434112</v>
       </c>
       <c r="P75">
-        <v>-33.845526576</v>
+        <v>-34.47054748800001</v>
       </c>
       <c r="Q75">
-        <v>-20.045526576</v>
+        <v>-20.67054748800001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3079108589838789</v>
+        <v>0.3179920458678742</v>
       </c>
       <c r="T75">
-        <v>3.416183167175717</v>
+        <v>3.547574827451706</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.08262561897453344</v>
+        <v>0.08150905655595864</v>
       </c>
       <c r="W75">
-        <v>0.216316879045805</v>
+        <v>0.216580164464105</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2582050592954169</v>
+        <v>0.2547158017373707</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.242947253629085</v>
+        <v>0.244847253629085</v>
       </c>
       <c r="C76">
-        <v>-92.08340590828982</v>
+        <v>-97.11319911149599</v>
       </c>
       <c r="D76">
-        <v>118.5685940917102</v>
+        <v>117.436800888504</v>
       </c>
       <c r="E76">
-        <v>277.352</v>
+        <v>281.25</v>
       </c>
       <c r="F76">
-        <v>288.452</v>
+        <v>292.35</v>
       </c>
       <c r="G76">
         <v>77.8</v>
@@ -7519,37 +7519,37 @@
         <v>17.325</v>
       </c>
       <c r="M76">
-        <v>68.01698160000001</v>
+        <v>68.93613000000001</v>
       </c>
       <c r="N76">
-        <v>-50.69198160000001</v>
+        <v>-51.61113000000001</v>
       </c>
       <c r="O76">
-        <v>-16.221434112</v>
+        <v>-16.51556160000001</v>
       </c>
       <c r="P76">
-        <v>-34.47054748800001</v>
+        <v>-35.0955684</v>
       </c>
       <c r="Q76">
-        <v>-20.67054748800001</v>
+        <v>-21.2955684</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3179920458678742</v>
+        <v>0.3288797277025892</v>
       </c>
       <c r="T76">
-        <v>3.547574827451706</v>
+        <v>3.689477820549774</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08150905655595864</v>
+        <v>0.08042226913521253</v>
       </c>
       <c r="W76">
-        <v>0.216580164464105</v>
+        <v>0.2168364289379169</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2547158017373707</v>
+        <v>0.2513195910475391</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.244847253629085</v>
+        <v>0.246747253629085</v>
       </c>
       <c r="C77">
-        <v>-97.11319911149599</v>
+        <v>-102.1215896127765</v>
       </c>
       <c r="D77">
-        <v>117.436800888504</v>
+        <v>116.3264103872234</v>
       </c>
       <c r="E77">
-        <v>281.25</v>
+        <v>285.148</v>
       </c>
       <c r="F77">
-        <v>292.35</v>
+        <v>296.248</v>
       </c>
       <c r="G77">
         <v>77.8</v>
@@ -7601,37 +7601,37 @@
         <v>17.325</v>
       </c>
       <c r="M77">
-        <v>68.93613000000001</v>
+        <v>69.8552784</v>
       </c>
       <c r="N77">
-        <v>-51.61113000000001</v>
+        <v>-52.53027840000001</v>
       </c>
       <c r="O77">
-        <v>-16.51556160000001</v>
+        <v>-16.809689088</v>
       </c>
       <c r="P77">
-        <v>-35.0955684</v>
+        <v>-35.720589312</v>
       </c>
       <c r="Q77">
-        <v>-21.2955684</v>
+        <v>-21.920589312</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3288797277025892</v>
+        <v>0.3406747163568637</v>
       </c>
       <c r="T77">
-        <v>3.689477820549774</v>
+        <v>3.843206063072682</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08042226913521253</v>
+        <v>0.07936408138343341</v>
       </c>
       <c r="W77">
-        <v>0.2168364289379169</v>
+        <v>0.2170859496097864</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2513195910475391</v>
+        <v>0.2480127543232294</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.246747253629085</v>
+        <v>0.248647253629085</v>
       </c>
       <c r="C78">
-        <v>-102.1215896127765</v>
+        <v>-107.1091788272299</v>
       </c>
       <c r="D78">
-        <v>116.3264103872234</v>
+        <v>115.2368211727701</v>
       </c>
       <c r="E78">
-        <v>285.148</v>
+        <v>289.046</v>
       </c>
       <c r="F78">
-        <v>296.248</v>
+        <v>300.146</v>
       </c>
       <c r="G78">
         <v>77.8</v>
@@ -7683,37 +7683,37 @@
         <v>17.325</v>
       </c>
       <c r="M78">
-        <v>69.8552784</v>
+        <v>70.7744268</v>
       </c>
       <c r="N78">
-        <v>-52.53027840000001</v>
+        <v>-53.4494268</v>
       </c>
       <c r="O78">
-        <v>-16.809689088</v>
+        <v>-17.103816576</v>
       </c>
       <c r="P78">
-        <v>-35.720589312</v>
+        <v>-36.345610224</v>
       </c>
       <c r="Q78">
-        <v>-21.920589312</v>
+        <v>-22.545610224</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3406747163568637</v>
+        <v>0.3534953561984665</v>
       </c>
       <c r="T78">
-        <v>3.843206063072682</v>
+        <v>4.01030197885845</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.07936408138343341</v>
+        <v>0.07833337902780442</v>
       </c>
       <c r="W78">
-        <v>0.2170859496097864</v>
+        <v>0.2173289892252437</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2480127543232294</v>
+        <v>0.2447918094618888</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.248647253629085</v>
+        <v>0.250547253629085</v>
       </c>
       <c r="C79">
-        <v>-107.1091788272299</v>
+        <v>-112.0765458460663</v>
       </c>
       <c r="D79">
-        <v>115.2368211727701</v>
+        <v>114.1674541539337</v>
       </c>
       <c r="E79">
-        <v>289.046</v>
+        <v>292.944</v>
       </c>
       <c r="F79">
-        <v>300.146</v>
+        <v>304.044</v>
       </c>
       <c r="G79">
         <v>77.8</v>
@@ -7765,37 +7765,37 @@
         <v>17.325</v>
       </c>
       <c r="M79">
-        <v>70.7744268</v>
+        <v>71.69357520000001</v>
       </c>
       <c r="N79">
-        <v>-53.4494268</v>
+        <v>-54.36857520000002</v>
       </c>
       <c r="O79">
-        <v>-17.103816576</v>
+        <v>-17.397944064</v>
       </c>
       <c r="P79">
-        <v>-36.345610224</v>
+        <v>-36.97063113600001</v>
       </c>
       <c r="Q79">
-        <v>-22.545610224</v>
+        <v>-23.17063113600001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3534953561984665</v>
+        <v>0.3674815087529423</v>
       </c>
       <c r="T79">
-        <v>4.01030197885845</v>
+        <v>4.192588432442927</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.07833337902780442</v>
+        <v>0.07732910493770435</v>
       </c>
       <c r="W79">
-        <v>0.2173289892252437</v>
+        <v>0.2175657970556893</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2447918094618888</v>
+        <v>0.241653452930326</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.250547253629085</v>
+        <v>0.252447253629085</v>
       </c>
       <c r="C80">
-        <v>-112.0765458460663</v>
+        <v>-117.0242484628831</v>
       </c>
       <c r="D80">
-        <v>114.1674541539337</v>
+        <v>113.1177515371169</v>
       </c>
       <c r="E80">
-        <v>292.944</v>
+        <v>296.842</v>
       </c>
       <c r="F80">
-        <v>304.044</v>
+        <v>307.942</v>
       </c>
       <c r="G80">
         <v>77.8</v>
@@ -7847,37 +7847,37 @@
         <v>17.325</v>
       </c>
       <c r="M80">
-        <v>71.69357520000001</v>
+        <v>72.61272360000001</v>
       </c>
       <c r="N80">
-        <v>-54.36857520000002</v>
+        <v>-55.28772360000001</v>
       </c>
       <c r="O80">
-        <v>-17.397944064</v>
+        <v>-17.69207155200001</v>
       </c>
       <c r="P80">
-        <v>-36.97063113600001</v>
+        <v>-37.59565204800001</v>
       </c>
       <c r="Q80">
-        <v>-23.17063113600001</v>
+        <v>-23.795652048</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3674815087529423</v>
+        <v>0.3827996758364158</v>
       </c>
       <c r="T80">
-        <v>4.192588432442927</v>
+        <v>4.392235500654494</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.07732910493770435</v>
+        <v>0.07635025550811315</v>
       </c>
       <c r="W80">
-        <v>0.2175657970556893</v>
+        <v>0.2177966097511869</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.241653452930326</v>
+        <v>0.2385945484628536</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.252447253629085</v>
+        <v>0.2543472536290849</v>
       </c>
       <c r="C81">
-        <v>-117.0242484628831</v>
+        <v>-121.9528241438402</v>
       </c>
       <c r="D81">
-        <v>113.1177515371169</v>
+        <v>112.0871758561598</v>
       </c>
       <c r="E81">
-        <v>296.842</v>
+        <v>300.74</v>
       </c>
       <c r="F81">
-        <v>307.942</v>
+        <v>311.84</v>
       </c>
       <c r="G81">
         <v>77.8</v>
@@ -7929,37 +7929,37 @@
         <v>17.325</v>
       </c>
       <c r="M81">
-        <v>72.61272360000001</v>
+        <v>73.53187200000001</v>
       </c>
       <c r="N81">
-        <v>-55.28772360000001</v>
+        <v>-56.20687200000001</v>
       </c>
       <c r="O81">
-        <v>-17.69207155200001</v>
+        <v>-17.98619904</v>
       </c>
       <c r="P81">
-        <v>-37.59565204800001</v>
+        <v>-38.22067296000001</v>
       </c>
       <c r="Q81">
-        <v>-23.795652048</v>
+        <v>-24.42067296000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3827996758364158</v>
+        <v>0.3996496596282366</v>
       </c>
       <c r="T81">
-        <v>4.392235500654494</v>
+        <v>4.611847275687219</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.07635025550811315</v>
+        <v>0.07539587731426174</v>
       </c>
       <c r="W81">
-        <v>0.2177966097511869</v>
+        <v>0.2180216521292971</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2385945484628536</v>
+        <v>0.2356121166070679</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2543472536290849</v>
+        <v>0.256247253629085</v>
       </c>
       <c r="C82">
-        <v>-121.9528241438402</v>
+        <v>-126.8627909452795</v>
       </c>
       <c r="D82">
-        <v>112.0871758561598</v>
+        <v>111.0752090547205</v>
       </c>
       <c r="E82">
-        <v>300.74</v>
+        <v>304.638</v>
       </c>
       <c r="F82">
-        <v>311.84</v>
+        <v>315.7380000000001</v>
       </c>
       <c r="G82">
         <v>77.8</v>
@@ -8011,37 +8011,37 @@
         <v>17.325</v>
       </c>
       <c r="M82">
-        <v>73.53187200000001</v>
+        <v>74.45102040000002</v>
       </c>
       <c r="N82">
-        <v>-56.20687200000001</v>
+        <v>-57.12602040000002</v>
       </c>
       <c r="O82">
-        <v>-17.98619904</v>
+        <v>-18.28032652800001</v>
       </c>
       <c r="P82">
-        <v>-38.22067296000001</v>
+        <v>-38.84569387200001</v>
       </c>
       <c r="Q82">
-        <v>-24.42067296000001</v>
+        <v>-25.04569387200001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3996496596282366</v>
+        <v>0.4182733259244595</v>
       </c>
       <c r="T82">
-        <v>4.611847275687219</v>
+        <v>4.854576079670757</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07539587731426174</v>
+        <v>0.07446506401408566</v>
       </c>
       <c r="W82">
-        <v>0.2180216521292971</v>
+        <v>0.2182411379054786</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2356121166070679</v>
+        <v>0.2327033250440177</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.256247253629085</v>
+        <v>0.258147253629085</v>
       </c>
       <c r="C83">
-        <v>-126.8627909452795</v>
+        <v>-131.7546483820825</v>
       </c>
       <c r="D83">
-        <v>111.0752090547205</v>
+        <v>110.0813516179175</v>
       </c>
       <c r="E83">
-        <v>304.638</v>
+        <v>308.536</v>
       </c>
       <c r="F83">
-        <v>315.7380000000001</v>
+        <v>319.636</v>
       </c>
       <c r="G83">
         <v>77.8</v>
@@ -8093,37 +8093,37 @@
         <v>17.325</v>
       </c>
       <c r="M83">
-        <v>74.45102040000002</v>
+        <v>75.3701688</v>
       </c>
       <c r="N83">
-        <v>-57.12602040000002</v>
+        <v>-58.04516880000001</v>
       </c>
       <c r="O83">
-        <v>-18.28032652800001</v>
+        <v>-18.574454016</v>
       </c>
       <c r="P83">
-        <v>-38.84569387200001</v>
+        <v>-39.47071478400001</v>
       </c>
       <c r="Q83">
-        <v>-25.04569387200001</v>
+        <v>-25.67071478400001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4182733259244595</v>
+        <v>0.4389662884758185</v>
       </c>
       <c r="T83">
-        <v>4.854576079670757</v>
+        <v>5.124274750763577</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07446506401408566</v>
+        <v>0.07355695347732853</v>
       </c>
       <c r="W83">
-        <v>0.2182411379054786</v>
+        <v>0.2184552703700459</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2327033250440177</v>
+        <v>0.2298654796166517</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.258147253629085</v>
+        <v>0.260047253629085</v>
       </c>
       <c r="C84">
-        <v>-131.7546483820825</v>
+        <v>-136.6288782498228</v>
       </c>
       <c r="D84">
-        <v>110.0813516179175</v>
+        <v>109.1051217501772</v>
       </c>
       <c r="E84">
-        <v>308.536</v>
+        <v>312.434</v>
       </c>
       <c r="F84">
-        <v>319.636</v>
+        <v>323.534</v>
       </c>
       <c r="G84">
         <v>77.8</v>
@@ -8175,37 +8175,37 @@
         <v>17.325</v>
       </c>
       <c r="M84">
-        <v>75.3701688</v>
+        <v>76.28931720000001</v>
       </c>
       <c r="N84">
-        <v>-58.04516880000001</v>
+        <v>-58.96431720000002</v>
       </c>
       <c r="O84">
-        <v>-18.574454016</v>
+        <v>-18.86858150400001</v>
       </c>
       <c r="P84">
-        <v>-39.47071478400001</v>
+        <v>-40.09573569600001</v>
       </c>
       <c r="Q84">
-        <v>-25.67071478400001</v>
+        <v>-26.29573569600001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4389662884758185</v>
+        <v>0.4620937172096901</v>
       </c>
       <c r="T84">
-        <v>5.124274750763577</v>
+        <v>5.425702677279082</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07355695347732853</v>
+        <v>0.07267072512217998</v>
       </c>
       <c r="W84">
-        <v>0.2184552703700459</v>
+        <v>0.21866424301619</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2298654796166517</v>
+        <v>0.2270960160068125</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.260047253629085</v>
+        <v>0.261947253629085</v>
       </c>
       <c r="C85">
-        <v>-136.6288782498228</v>
+        <v>-141.4859454035562</v>
       </c>
       <c r="D85">
-        <v>109.1051217501772</v>
+        <v>108.1460545964438</v>
       </c>
       <c r="E85">
-        <v>312.434</v>
+        <v>316.332</v>
       </c>
       <c r="F85">
-        <v>323.534</v>
+        <v>327.432</v>
       </c>
       <c r="G85">
         <v>77.8</v>
@@ -8257,37 +8257,37 @@
         <v>17.325</v>
       </c>
       <c r="M85">
-        <v>76.28931720000001</v>
+        <v>77.20846560000001</v>
       </c>
       <c r="N85">
-        <v>-58.96431720000002</v>
+        <v>-59.88346560000002</v>
       </c>
       <c r="O85">
-        <v>-18.86858150400001</v>
+        <v>-19.16270899200001</v>
       </c>
       <c r="P85">
-        <v>-40.09573569600001</v>
+        <v>-40.72075660800001</v>
       </c>
       <c r="Q85">
-        <v>-26.29573569600001</v>
+        <v>-26.92075660800001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4620937172096901</v>
+        <v>0.4881120745352959</v>
       </c>
       <c r="T85">
-        <v>5.425702677279082</v>
+        <v>5.764809094609026</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07267072512217998</v>
+        <v>0.07180559744215403</v>
       </c>
       <c r="W85">
-        <v>0.21866424301619</v>
+        <v>0.2188682401231401</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2270960160068125</v>
+        <v>0.2243924920067314</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2619472536290849</v>
+        <v>0.263847253629085</v>
       </c>
       <c r="C86">
-        <v>-141.4859454035562</v>
+        <v>-146.3262984958945</v>
       </c>
       <c r="D86">
-        <v>108.1460545964438</v>
+        <v>107.2037015041055</v>
       </c>
       <c r="E86">
-        <v>316.332</v>
+        <v>320.23</v>
       </c>
       <c r="F86">
-        <v>327.432</v>
+        <v>331.33</v>
       </c>
       <c r="G86">
         <v>77.8</v>
@@ -8339,37 +8339,37 @@
         <v>17.325</v>
       </c>
       <c r="M86">
-        <v>77.20846560000001</v>
+        <v>78.12761399999999</v>
       </c>
       <c r="N86">
-        <v>-59.88346560000002</v>
+        <v>-60.802614</v>
       </c>
       <c r="O86">
-        <v>-19.16270899200001</v>
+        <v>-19.45683648</v>
       </c>
       <c r="P86">
-        <v>-40.72075660800001</v>
+        <v>-41.34577752</v>
       </c>
       <c r="Q86">
-        <v>-26.92075660800001</v>
+        <v>-27.54577752</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4881120745352956</v>
+        <v>0.5175995461709819</v>
       </c>
       <c r="T86">
-        <v>5.764809094609022</v>
+        <v>6.149129700916291</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07180559744215403</v>
+        <v>0.07096082570754048</v>
       </c>
       <c r="W86">
-        <v>0.2188682401231401</v>
+        <v>0.219067437298162</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2243924920067314</v>
+        <v>0.2217525803360639</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.263847253629085</v>
+        <v>0.265747253629085</v>
       </c>
       <c r="C87">
-        <v>-146.3262984958945</v>
+        <v>-151.1503706768243</v>
       </c>
       <c r="D87">
-        <v>107.2037015041055</v>
+        <v>106.2776293231757</v>
       </c>
       <c r="E87">
-        <v>320.23</v>
+        <v>324.128</v>
       </c>
       <c r="F87">
-        <v>331.33</v>
+        <v>335.228</v>
       </c>
       <c r="G87">
         <v>77.8</v>
@@ -8421,37 +8421,37 @@
         <v>17.325</v>
       </c>
       <c r="M87">
-        <v>78.12761399999999</v>
+        <v>79.04676240000001</v>
       </c>
       <c r="N87">
-        <v>-60.802614</v>
+        <v>-61.72176240000001</v>
       </c>
       <c r="O87">
-        <v>-19.45683648</v>
+        <v>-19.750963968</v>
       </c>
       <c r="P87">
-        <v>-41.34577752</v>
+        <v>-41.97079843200001</v>
       </c>
       <c r="Q87">
-        <v>-27.54577752</v>
+        <v>-28.17079843200001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5175995461709819</v>
+        <v>0.5512995137546236</v>
       </c>
       <c r="T87">
-        <v>6.149129700916291</v>
+        <v>6.588353250981741</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07096082570754048</v>
+        <v>0.07013569982722022</v>
       </c>
       <c r="W87">
-        <v>0.219067437298162</v>
+        <v>0.2192620019807415</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2217525803360639</v>
+        <v>0.2191740619600632</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.265747253629085</v>
+        <v>0.267647253629085</v>
       </c>
       <c r="C88">
-        <v>-151.1503706768243</v>
+        <v>-155.9585802575643</v>
       </c>
       <c r="D88">
-        <v>106.2776293231757</v>
+        <v>105.3674197424358</v>
       </c>
       <c r="E88">
-        <v>324.128</v>
+        <v>328.026</v>
       </c>
       <c r="F88">
-        <v>335.228</v>
+        <v>339.126</v>
       </c>
       <c r="G88">
         <v>77.8</v>
@@ -8503,37 +8503,37 @@
         <v>17.325</v>
       </c>
       <c r="M88">
-        <v>79.04676240000001</v>
+        <v>79.96591080000002</v>
       </c>
       <c r="N88">
-        <v>-61.72176240000001</v>
+        <v>-62.64091080000002</v>
       </c>
       <c r="O88">
-        <v>-19.750963968</v>
+        <v>-20.04509145600001</v>
       </c>
       <c r="P88">
-        <v>-41.97079843200001</v>
+        <v>-42.59581934400001</v>
       </c>
       <c r="Q88">
-        <v>-28.17079843200001</v>
+        <v>-28.79581934400001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5512995137546236</v>
+        <v>0.5901840917357484</v>
       </c>
       <c r="T88">
-        <v>6.588353250981741</v>
+        <v>7.095149654903413</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07013569982722022</v>
+        <v>0.06932954235794182</v>
       </c>
       <c r="W88">
-        <v>0.2192620019807415</v>
+        <v>0.2194520939119973</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2191740619600632</v>
+        <v>0.2166548198685682</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.267647253629085</v>
+        <v>0.2695472536290849</v>
       </c>
       <c r="C89">
-        <v>-155.9585802575643</v>
+        <v>-160.7513313405988</v>
       </c>
       <c r="D89">
-        <v>105.3674197424358</v>
+        <v>104.4726686594013</v>
       </c>
       <c r="E89">
-        <v>328.026</v>
+        <v>331.924</v>
       </c>
       <c r="F89">
-        <v>339.126</v>
+        <v>343.024</v>
       </c>
       <c r="G89">
         <v>77.8</v>
@@ -8585,37 +8585,37 @@
         <v>17.325</v>
       </c>
       <c r="M89">
-        <v>79.96591080000002</v>
+        <v>80.8850592</v>
       </c>
       <c r="N89">
-        <v>-62.64091080000002</v>
+        <v>-63.5600592</v>
       </c>
       <c r="O89">
-        <v>-20.04509145600001</v>
+        <v>-20.339218944</v>
       </c>
       <c r="P89">
-        <v>-42.59581934400001</v>
+        <v>-43.220840256</v>
       </c>
       <c r="Q89">
-        <v>-28.79581934400001</v>
+        <v>-29.420840256</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5901840917357484</v>
+        <v>0.6355494327137274</v>
       </c>
       <c r="T89">
-        <v>7.095149654903413</v>
+        <v>7.686412126145364</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.06932954235794182</v>
+        <v>0.06854170664932886</v>
       </c>
       <c r="W89">
-        <v>0.2194520939119973</v>
+        <v>0.2196378655720883</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2166548198685682</v>
+        <v>0.2141928332791527</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2695472536290849</v>
+        <v>0.271447253629085</v>
       </c>
       <c r="C90">
-        <v>-160.7513313405988</v>
+        <v>-165.5290144178816</v>
       </c>
       <c r="D90">
-        <v>104.4726686594013</v>
+        <v>103.5929855821184</v>
       </c>
       <c r="E90">
-        <v>331.924</v>
+        <v>335.822</v>
       </c>
       <c r="F90">
-        <v>343.024</v>
+        <v>346.922</v>
       </c>
       <c r="G90">
         <v>77.8</v>
@@ -8667,37 +8667,37 @@
         <v>17.325</v>
       </c>
       <c r="M90">
-        <v>80.8850592</v>
+        <v>81.80420760000001</v>
       </c>
       <c r="N90">
-        <v>-63.5600592</v>
+        <v>-64.47920760000002</v>
       </c>
       <c r="O90">
-        <v>-20.339218944</v>
+        <v>-20.63334643200001</v>
       </c>
       <c r="P90">
-        <v>-43.220840256</v>
+        <v>-43.84586116800001</v>
       </c>
       <c r="Q90">
-        <v>-29.420840256</v>
+        <v>-30.04586116800001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6355494327137274</v>
+        <v>0.6891630175058846</v>
       </c>
       <c r="T90">
-        <v>7.686412126145364</v>
+        <v>8.385176864885853</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.06854170664932886</v>
+        <v>0.06777157511394313</v>
       </c>
       <c r="W90">
-        <v>0.2196378655720883</v>
+        <v>0.2198194625881322</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2141928332791527</v>
+        <v>0.2117861722310722</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.271447253629085</v>
+        <v>0.273347253629085</v>
       </c>
       <c r="C91">
-        <v>-165.5290144178816</v>
+        <v>-170.2920069390696</v>
       </c>
       <c r="D91">
-        <v>103.5929855821184</v>
+        <v>102.7279930609304</v>
       </c>
       <c r="E91">
-        <v>335.822</v>
+        <v>339.72</v>
       </c>
       <c r="F91">
-        <v>346.922</v>
+        <v>350.82</v>
       </c>
       <c r="G91">
         <v>77.8</v>
@@ -8749,37 +8749,37 @@
         <v>17.325</v>
       </c>
       <c r="M91">
-        <v>81.80420760000001</v>
+        <v>82.723356</v>
       </c>
       <c r="N91">
-        <v>-64.47920760000002</v>
+        <v>-65.39835600000001</v>
       </c>
       <c r="O91">
-        <v>-20.63334643200001</v>
+        <v>-20.92747392</v>
       </c>
       <c r="P91">
-        <v>-43.84586116800001</v>
+        <v>-44.47088208</v>
       </c>
       <c r="Q91">
-        <v>-30.04586116800001</v>
+        <v>-30.67088208</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6891630175058846</v>
+        <v>0.7534993192564731</v>
       </c>
       <c r="T91">
-        <v>8.385176864885853</v>
+        <v>9.223694551374438</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.06777157511394313</v>
+        <v>0.06701855761267711</v>
       </c>
       <c r="W91">
-        <v>0.2198194625881322</v>
+        <v>0.2199970241149307</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2117861722310722</v>
+        <v>0.2094329925396159</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.273347253629085</v>
+        <v>0.275247253629085</v>
       </c>
       <c r="C92">
-        <v>-170.2920069390696</v>
+        <v>-175.0406738515239</v>
       </c>
       <c r="D92">
-        <v>102.7279930609304</v>
+        <v>101.8773261484761</v>
       </c>
       <c r="E92">
-        <v>339.72</v>
+        <v>343.618</v>
       </c>
       <c r="F92">
-        <v>350.82</v>
+        <v>354.718</v>
       </c>
       <c r="G92">
         <v>77.8</v>
@@ -8831,37 +8831,37 @@
         <v>17.325</v>
       </c>
       <c r="M92">
-        <v>82.723356</v>
+        <v>83.64250440000001</v>
       </c>
       <c r="N92">
-        <v>-65.39835600000001</v>
+        <v>-66.31750440000002</v>
       </c>
       <c r="O92">
-        <v>-20.92747392</v>
+        <v>-21.22160140800001</v>
       </c>
       <c r="P92">
-        <v>-44.47088208</v>
+        <v>-45.09590299200001</v>
       </c>
       <c r="Q92">
-        <v>-30.67088208</v>
+        <v>-31.29590299200001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7534993192564731</v>
+        <v>0.8321325769516369</v>
       </c>
       <c r="T92">
-        <v>9.223694551374438</v>
+        <v>10.24854950152715</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.06701855761267711</v>
+        <v>0.06628208994660373</v>
       </c>
       <c r="W92">
-        <v>0.2199970241149307</v>
+        <v>0.2201706831905909</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2094329925396159</v>
+        <v>0.2071315310831365</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.275247253629085</v>
+        <v>0.277147253629085</v>
       </c>
       <c r="C93">
-        <v>-175.0406738515239</v>
+        <v>-179.775368113702</v>
       </c>
       <c r="D93">
-        <v>101.8773261484761</v>
+        <v>101.0406318862981</v>
       </c>
       <c r="E93">
-        <v>343.618</v>
+        <v>347.516</v>
       </c>
       <c r="F93">
-        <v>354.718</v>
+        <v>358.616</v>
       </c>
       <c r="G93">
         <v>77.8</v>
@@ -8913,37 +8913,37 @@
         <v>17.325</v>
       </c>
       <c r="M93">
-        <v>83.64250440000001</v>
+        <v>84.56165280000002</v>
       </c>
       <c r="N93">
-        <v>-66.31750440000002</v>
+        <v>-67.23665280000003</v>
       </c>
       <c r="O93">
-        <v>-21.22160140800001</v>
+        <v>-21.51572889600001</v>
       </c>
       <c r="P93">
-        <v>-45.09590299200001</v>
+        <v>-45.72092390400002</v>
       </c>
       <c r="Q93">
-        <v>-31.29590299200001</v>
+        <v>-31.92092390400002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8321325769516369</v>
+        <v>0.9304241490705917</v>
       </c>
       <c r="T93">
-        <v>10.24854950152715</v>
+        <v>11.52961818921805</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06628208994660373</v>
+        <v>0.06556163244718412</v>
       </c>
       <c r="W93">
-        <v>0.2201706831905909</v>
+        <v>0.220340567068954</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2071315310831365</v>
+        <v>0.2048801013974503</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.277147253629085</v>
+        <v>0.279047253629085</v>
       </c>
       <c r="C94">
-        <v>-179.775368113702</v>
+        <v>-184.4964311834573</v>
       </c>
       <c r="D94">
-        <v>101.0406318862981</v>
+        <v>100.2175688165427</v>
       </c>
       <c r="E94">
-        <v>347.516</v>
+        <v>351.414</v>
       </c>
       <c r="F94">
-        <v>358.616</v>
+        <v>362.514</v>
       </c>
       <c r="G94">
         <v>77.8</v>
@@ -8995,37 +8995,37 @@
         <v>17.325</v>
       </c>
       <c r="M94">
-        <v>84.56165280000002</v>
+        <v>85.4808012</v>
       </c>
       <c r="N94">
-        <v>-67.23665280000003</v>
+        <v>-68.15580120000001</v>
       </c>
       <c r="O94">
-        <v>-21.51572889600001</v>
+        <v>-21.809856384</v>
       </c>
       <c r="P94">
-        <v>-45.72092390400002</v>
+        <v>-46.34594481600001</v>
       </c>
       <c r="Q94">
-        <v>-31.92092390400002</v>
+        <v>-32.54594481600002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9304241490705917</v>
+        <v>1.056799027509248</v>
       </c>
       <c r="T94">
-        <v>11.52961818921805</v>
+        <v>13.17670650196349</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06556163244718412</v>
+        <v>0.06485666865742946</v>
       </c>
       <c r="W94">
-        <v>0.220340567068954</v>
+        <v>0.2205067975305781</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2048801013974503</v>
+        <v>0.2026770895544669</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.279047253629085</v>
+        <v>0.280947253629085</v>
       </c>
       <c r="C95">
-        <v>-184.4964311834573</v>
+        <v>-189.2041934826666</v>
       </c>
       <c r="D95">
-        <v>100.2175688165427</v>
+        <v>99.40780651733343</v>
       </c>
       <c r="E95">
-        <v>351.414</v>
+        <v>355.312</v>
       </c>
       <c r="F95">
-        <v>362.514</v>
+        <v>366.412</v>
       </c>
       <c r="G95">
         <v>77.8</v>
@@ -9077,37 +9077,37 @@
         <v>17.325</v>
       </c>
       <c r="M95">
-        <v>85.4808012</v>
+        <v>86.39994960000001</v>
       </c>
       <c r="N95">
-        <v>-68.15580120000001</v>
+        <v>-69.07494960000002</v>
       </c>
       <c r="O95">
-        <v>-21.809856384</v>
+        <v>-22.10398387200001</v>
       </c>
       <c r="P95">
-        <v>-46.34594481600001</v>
+        <v>-46.97096572800002</v>
       </c>
       <c r="Q95">
-        <v>-32.54594481600002</v>
+        <v>-33.17096572800001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.056799027509248</v>
+        <v>1.225298865427456</v>
       </c>
       <c r="T95">
-        <v>13.17670650196349</v>
+        <v>15.37282425229074</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06485666865742946</v>
+        <v>0.06416670409724402</v>
       </c>
       <c r="W95">
-        <v>0.2205067975305781</v>
+        <v>0.2206694911738699</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2026770895544669</v>
+        <v>0.2005209503038875</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.280947253629085</v>
+        <v>0.282847253629085</v>
       </c>
       <c r="C96">
-        <v>-189.2041934826666</v>
+        <v>-193.8989748395115</v>
       </c>
       <c r="D96">
-        <v>99.40780651733343</v>
+        <v>98.61102516048852</v>
       </c>
       <c r="E96">
-        <v>355.312</v>
+        <v>359.21</v>
       </c>
       <c r="F96">
-        <v>366.412</v>
+        <v>370.3100000000001</v>
       </c>
       <c r="G96">
         <v>77.8</v>
@@ -9159,37 +9159,37 @@
         <v>17.325</v>
       </c>
       <c r="M96">
-        <v>86.39994960000001</v>
+        <v>87.31909800000001</v>
       </c>
       <c r="N96">
-        <v>-69.07494960000002</v>
+        <v>-69.99409800000001</v>
       </c>
       <c r="O96">
-        <v>-22.10398387200001</v>
+        <v>-22.39811136</v>
       </c>
       <c r="P96">
-        <v>-46.97096572800002</v>
+        <v>-47.59598664000001</v>
       </c>
       <c r="Q96">
-        <v>-33.17096572800001</v>
+        <v>-33.79598664000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.225298865427456</v>
+        <v>1.461198638512948</v>
       </c>
       <c r="T96">
-        <v>15.37282425229074</v>
+        <v>18.4473891027489</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06416670409724402</v>
+        <v>0.06349126510674673</v>
       </c>
       <c r="W96">
-        <v>0.2206694911738699</v>
+        <v>0.2208287596878291</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2005209503038875</v>
+        <v>0.1984102034585836</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.282847253629085</v>
+        <v>0.284747253629085</v>
       </c>
       <c r="C97">
-        <v>-193.8989748395115</v>
+        <v>-198.5810849096601</v>
       </c>
       <c r="D97">
-        <v>98.61102516048852</v>
+        <v>97.82691509033988</v>
       </c>
       <c r="E97">
-        <v>359.21</v>
+        <v>363.108</v>
       </c>
       <c r="F97">
-        <v>370.3100000000001</v>
+        <v>374.208</v>
       </c>
       <c r="G97">
         <v>77.8</v>
@@ -9241,37 +9241,37 @@
         <v>17.325</v>
       </c>
       <c r="M97">
-        <v>87.31909800000001</v>
+        <v>88.23824640000001</v>
       </c>
       <c r="N97">
-        <v>-69.99409800000001</v>
+        <v>-70.91324640000002</v>
       </c>
       <c r="O97">
-        <v>-22.39811136</v>
+        <v>-22.69223884800001</v>
       </c>
       <c r="P97">
-        <v>-47.59598664000001</v>
+        <v>-48.22100755200002</v>
       </c>
       <c r="Q97">
-        <v>-33.79598664000001</v>
+        <v>-34.42100755200002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.461198638512948</v>
+        <v>1.815048298141186</v>
       </c>
       <c r="T97">
-        <v>18.4473891027489</v>
+        <v>23.05923637843614</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06349126510674673</v>
+        <v>0.06282989776188479</v>
       </c>
       <c r="W97">
-        <v>0.2208287596878291</v>
+        <v>0.2209847101077476</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1984102034585836</v>
+        <v>0.1963434305058899</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2847472536290849</v>
+        <v>0.2866472536290849</v>
       </c>
       <c r="C98">
-        <v>-198.5810849096601</v>
+        <v>-203.2508235775126</v>
       </c>
       <c r="D98">
-        <v>97.82691509033991</v>
+        <v>97.05517642248739</v>
       </c>
       <c r="E98">
-        <v>363.1079999999999</v>
+        <v>367.006</v>
       </c>
       <c r="F98">
-        <v>374.208</v>
+        <v>378.106</v>
       </c>
       <c r="G98">
         <v>77.8</v>
@@ -9323,37 +9323,37 @@
         <v>17.325</v>
       </c>
       <c r="M98">
-        <v>88.23824639999999</v>
+        <v>89.15739480000001</v>
       </c>
       <c r="N98">
-        <v>-70.91324639999999</v>
+        <v>-71.8323948</v>
       </c>
       <c r="O98">
-        <v>-22.692238848</v>
+        <v>-22.986366336</v>
       </c>
       <c r="P98">
-        <v>-48.22100755199999</v>
+        <v>-48.846028464</v>
       </c>
       <c r="Q98">
-        <v>-34.42100755199999</v>
+        <v>-35.046028464</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.815048298141181</v>
+        <v>2.404797730854908</v>
       </c>
       <c r="T98">
-        <v>23.05923637843607</v>
+        <v>30.74564850458143</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0628298977618848</v>
+        <v>0.06218216685712309</v>
       </c>
       <c r="W98">
-        <v>0.2209847101077476</v>
+        <v>0.2211374450550904</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1963434305058901</v>
+        <v>0.1943192714285097</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2866472536290849</v>
+        <v>0.288547253629085</v>
       </c>
       <c r="C99">
-        <v>-203.2508235775126</v>
+        <v>-207.9084813386031</v>
       </c>
       <c r="D99">
-        <v>97.05517642248739</v>
+        <v>96.29551866139693</v>
       </c>
       <c r="E99">
-        <v>367.006</v>
+        <v>370.904</v>
       </c>
       <c r="F99">
-        <v>378.106</v>
+        <v>382.004</v>
       </c>
       <c r="G99">
         <v>77.8</v>
@@ -9405,37 +9405,37 @@
         <v>17.325</v>
       </c>
       <c r="M99">
-        <v>89.15739480000001</v>
+        <v>90.0765432</v>
       </c>
       <c r="N99">
-        <v>-71.8323948</v>
+        <v>-72.75154320000001</v>
       </c>
       <c r="O99">
-        <v>-22.986366336</v>
+        <v>-23.280493824</v>
       </c>
       <c r="P99">
-        <v>-48.846028464</v>
+        <v>-49.47104937600001</v>
       </c>
       <c r="Q99">
-        <v>-35.046028464</v>
+        <v>-35.67104937600001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.404797730854908</v>
+        <v>3.584296596282362</v>
       </c>
       <c r="T99">
-        <v>30.74564850458143</v>
+        <v>46.11847275687215</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06218216685712309</v>
+        <v>0.06154765495041775</v>
       </c>
       <c r="W99">
-        <v>0.2211374450550904</v>
+        <v>0.2212870629626915</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1943192714285097</v>
+        <v>0.1923364217200554</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.288547253629085</v>
+        <v>0.290447253629085</v>
       </c>
       <c r="C100">
-        <v>-207.9084813386031</v>
+        <v>-212.5543396641825</v>
       </c>
       <c r="D100">
-        <v>96.29551866139693</v>
+        <v>95.54766033581753</v>
       </c>
       <c r="E100">
-        <v>370.904</v>
+        <v>374.802</v>
       </c>
       <c r="F100">
-        <v>382.004</v>
+        <v>385.902</v>
       </c>
       <c r="G100">
         <v>77.8</v>
@@ -9487,37 +9487,37 @@
         <v>17.325</v>
       </c>
       <c r="M100">
-        <v>90.0765432</v>
+        <v>90.9956916</v>
       </c>
       <c r="N100">
-        <v>-72.75154320000001</v>
+        <v>-73.6706916</v>
       </c>
       <c r="O100">
-        <v>-23.280493824</v>
+        <v>-23.574621312</v>
       </c>
       <c r="P100">
-        <v>-49.47104937600001</v>
+        <v>-50.09607028799999</v>
       </c>
       <c r="Q100">
-        <v>-35.67104937600001</v>
+        <v>-36.296070288</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.584296596282362</v>
+        <v>7.122793192564724</v>
       </c>
       <c r="T100">
-        <v>46.11847275687215</v>
+        <v>92.23694551374429</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06154765495041775</v>
+        <v>0.0609259614660701</v>
       </c>
       <c r="W100">
-        <v>0.2212870629626915</v>
+        <v>0.2214336582863007</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1923364217200554</v>
+        <v>0.1903936295814691</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.290447253629085</v>
-      </c>
-      <c r="C101">
-        <v>-212.5543396641825</v>
-      </c>
-      <c r="D101">
-        <v>95.54766033581753</v>
-      </c>
-      <c r="E101">
-        <v>374.802</v>
-      </c>
-      <c r="F101">
-        <v>385.902</v>
-      </c>
-      <c r="G101">
-        <v>77.8</v>
-      </c>
-      <c r="H101">
-        <v>378.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>31.125</v>
-      </c>
-      <c r="K101">
-        <v>13.8</v>
-      </c>
-      <c r="L101">
-        <v>17.325</v>
-      </c>
-      <c r="M101">
-        <v>90.9956916</v>
-      </c>
-      <c r="N101">
-        <v>-73.6706916</v>
-      </c>
-      <c r="O101">
-        <v>-23.574621312</v>
-      </c>
-      <c r="P101">
-        <v>-50.09607028799999</v>
-      </c>
-      <c r="Q101">
-        <v>-36.296070288</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.122793192564724</v>
-      </c>
-      <c r="T101">
-        <v>92.23694551374429</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0609259614660701</v>
-      </c>
-      <c r="W101">
-        <v>0.2214336582863007</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1903936295814691</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
